--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1271"/>
+  <dimension ref="A1:K1521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34795,7 +34795,7 @@
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
-        <v>46151.31814837972</v>
+        <v>46151.31814837963</v>
       </c>
       <c r="B1252" t="n">
         <v>8.959</v>
@@ -34807,7 +34807,7 @@
       </c>
       <c r="D1252" t="inlineStr"/>
       <c r="E1252" t="inlineStr"/>
-      <c r="F1252" t="b">
+      <c r="F1252" t="n">
         <v>0</v>
       </c>
       <c r="G1252" t="inlineStr"/>
@@ -34822,7 +34822,7 @@
     </row>
     <row r="1253">
       <c r="A1253" s="1" t="n">
-        <v>46151.31815640538</v>
+        <v>46151.31815640046</v>
       </c>
       <c r="B1253" t="n">
         <v>9.653</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="D1253" t="inlineStr"/>
       <c r="E1253" t="inlineStr"/>
-      <c r="F1253" t="b">
+      <c r="F1253" t="n">
         <v>1</v>
       </c>
       <c r="G1253" t="inlineStr"/>
@@ -34849,7 +34849,7 @@
     </row>
     <row r="1254">
       <c r="A1254" s="1" t="n">
-        <v>46151.31822971688</v>
+        <v>46151.31822972222</v>
       </c>
       <c r="B1254" t="n">
         <v>15.987</v>
@@ -34861,7 +34861,7 @@
       </c>
       <c r="D1254" t="inlineStr"/>
       <c r="E1254" t="inlineStr"/>
-      <c r="F1254" t="b">
+      <c r="F1254" t="n">
         <v>1</v>
       </c>
       <c r="G1254" t="inlineStr"/>
@@ -34876,7 +34876,7 @@
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
-        <v>46151.31826831341</v>
+        <v>46151.31826831018</v>
       </c>
       <c r="B1255" t="n">
         <v>19.321</v>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="D1255" t="inlineStr"/>
       <c r="E1255" t="inlineStr"/>
-      <c r="F1255" t="b">
+      <c r="F1255" t="n">
         <v>1</v>
       </c>
       <c r="G1255" t="inlineStr"/>
@@ -34903,7 +34903,7 @@
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
-        <v>46151.31827388406</v>
+        <v>46151.31827388889</v>
       </c>
       <c r="B1256" t="n">
         <v>19.802</v>
@@ -34915,7 +34915,7 @@
       </c>
       <c r="D1256" t="inlineStr"/>
       <c r="E1256" t="inlineStr"/>
-      <c r="F1256" t="b">
+      <c r="F1256" t="n">
         <v>1</v>
       </c>
       <c r="G1256" t="inlineStr"/>
@@ -34930,7 +34930,7 @@
     </row>
     <row r="1257">
       <c r="A1257" s="1" t="n">
-        <v>46151.31827781712</v>
+        <v>46151.3182778125</v>
       </c>
       <c r="B1257" t="n">
         <v>20.142</v>
@@ -34942,7 +34942,7 @@
       </c>
       <c r="D1257" t="inlineStr"/>
       <c r="E1257" t="inlineStr"/>
-      <c r="F1257" t="b">
+      <c r="F1257" t="n">
         <v>1</v>
       </c>
       <c r="G1257" t="inlineStr"/>
@@ -34957,7 +34957,7 @@
     </row>
     <row r="1258">
       <c r="A1258" s="1" t="n">
-        <v>46151.31828175573</v>
+        <v>46151.31828175926</v>
       </c>
       <c r="B1258" t="n">
         <v>20.483</v>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="inlineStr"/>
-      <c r="F1258" t="b">
+      <c r="F1258" t="n">
         <v>1</v>
       </c>
       <c r="G1258" t="inlineStr"/>
@@ -34984,7 +34984,7 @@
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
-        <v>46151.31835458361</v>
+        <v>46151.31835458333</v>
       </c>
       <c r="B1259" t="n">
         <v>26.775</v>
@@ -34996,7 +34996,7 @@
       </c>
       <c r="D1259" t="inlineStr"/>
       <c r="E1259" t="inlineStr"/>
-      <c r="F1259" t="b">
+      <c r="F1259" t="n">
         <v>1</v>
       </c>
       <c r="G1259" t="inlineStr"/>
@@ -35011,7 +35011,7 @@
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
-        <v>46151.31835791596</v>
+        <v>46151.31835791667</v>
       </c>
       <c r="B1260" t="n">
         <v>27.063</v>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="D1260" t="inlineStr"/>
       <c r="E1260" t="inlineStr"/>
-      <c r="F1260" t="b">
+      <c r="F1260" t="n">
         <v>1</v>
       </c>
       <c r="G1260" t="inlineStr"/>
@@ -35038,7 +35038,7 @@
     </row>
     <row r="1261">
       <c r="A1261" s="1" t="n">
-        <v>46151.31841055334</v>
+        <v>46151.31841055556</v>
       </c>
       <c r="B1261" t="n">
         <v>31.611</v>
@@ -35050,7 +35050,7 @@
       </c>
       <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="inlineStr"/>
-      <c r="F1261" t="b">
+      <c r="F1261" t="n">
         <v>1</v>
       </c>
       <c r="G1261" t="inlineStr"/>
@@ -35065,7 +35065,7 @@
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
-        <v>46151.31841807183</v>
+        <v>46151.31841806713</v>
       </c>
       <c r="B1262" t="n">
         <v>32.261</v>
@@ -35077,7 +35077,7 @@
       </c>
       <c r="D1262" t="inlineStr"/>
       <c r="E1262" t="inlineStr"/>
-      <c r="F1262" t="b">
+      <c r="F1262" t="n">
         <v>1</v>
       </c>
       <c r="G1262" t="inlineStr"/>
@@ -35092,7 +35092,7 @@
     </row>
     <row r="1263">
       <c r="A1263" s="1" t="n">
-        <v>46151.31842072679</v>
+        <v>46151.31842072916</v>
       </c>
       <c r="B1263" t="n">
         <v>32.49</v>
@@ -35111,7 +35111,7 @@
         <v>0.2</v>
       </c>
       <c r="F1263" t="inlineStr"/>
-      <c r="G1263" t="b">
+      <c r="G1263" t="n">
         <v>1</v>
       </c>
       <c r="H1263" t="n">
@@ -35125,7 +35125,7 @@
     </row>
     <row r="1264">
       <c r="A1264" s="1" t="n">
-        <v>46151.31843305603</v>
+        <v>46151.31843305555</v>
       </c>
       <c r="B1264" t="n">
         <v>33.555</v>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="inlineStr"/>
-      <c r="F1264" t="b">
+      <c r="F1264" t="n">
         <v>0</v>
       </c>
       <c r="G1264" t="inlineStr"/>
@@ -35152,7 +35152,7 @@
     </row>
     <row r="1265">
       <c r="A1265" s="1" t="n">
-        <v>46151.31844063041</v>
+        <v>46151.318440625</v>
       </c>
       <c r="B1265" t="n">
         <v>34.21</v>
@@ -35164,7 +35164,7 @@
       </c>
       <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="inlineStr"/>
-      <c r="F1265" t="b">
+      <c r="F1265" t="n">
         <v>0</v>
       </c>
       <c r="G1265" t="inlineStr"/>
@@ -35179,7 +35179,7 @@
     </row>
     <row r="1266">
       <c r="A1266" s="1" t="n">
-        <v>46151.31847797339</v>
+        <v>46151.31847797454</v>
       </c>
       <c r="B1266" t="n">
         <v>37.437</v>
@@ -35191,7 +35191,7 @@
       </c>
       <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="inlineStr"/>
-      <c r="F1266" t="b">
+      <c r="F1266" t="n">
         <v>1</v>
       </c>
       <c r="G1266" t="inlineStr"/>
@@ -35206,7 +35206,7 @@
     </row>
     <row r="1267">
       <c r="A1267" s="1" t="n">
-        <v>46151.31851477919</v>
+        <v>46151.31851478009</v>
       </c>
       <c r="B1267" t="n">
         <v>40.617</v>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="inlineStr"/>
-      <c r="F1267" t="b">
+      <c r="F1267" t="n">
         <v>1</v>
       </c>
       <c r="G1267" t="inlineStr"/>
@@ -35233,7 +35233,7 @@
     </row>
     <row r="1268">
       <c r="A1268" s="1" t="n">
-        <v>46151.31851867386</v>
+        <v>46151.31851866898</v>
       </c>
       <c r="B1268" t="n">
         <v>40.953</v>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="inlineStr"/>
-      <c r="F1268" t="b">
+      <c r="F1268" t="n">
         <v>1</v>
       </c>
       <c r="G1268" t="inlineStr"/>
@@ -35260,7 +35260,7 @@
     </row>
     <row r="1269">
       <c r="A1269" s="1" t="n">
-        <v>46151.31852222391</v>
+        <v>46151.31852222222</v>
       </c>
       <c r="B1269" t="n">
         <v>41.26</v>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="inlineStr"/>
-      <c r="F1269" t="b">
+      <c r="F1269" t="n">
         <v>1</v>
       </c>
       <c r="G1269" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
     </row>
     <row r="1270">
       <c r="A1270" s="1" t="n">
-        <v>46151.3185255619</v>
+        <v>46151.31852556713</v>
       </c>
       <c r="B1270" t="n">
         <v>41.548</v>
@@ -35299,7 +35299,7 @@
       </c>
       <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="inlineStr"/>
-      <c r="F1270" t="b">
+      <c r="F1270" t="n">
         <v>1</v>
       </c>
       <c r="G1270" t="inlineStr"/>
@@ -35314,7 +35314,7 @@
     </row>
     <row r="1271">
       <c r="A1271" s="1" t="n">
-        <v>46151.31804468211</v>
+        <v>46151.3180446875</v>
       </c>
       <c r="B1271" t="n">
         <v>41.581</v>
@@ -35327,7 +35327,7 @@
       <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="inlineStr"/>
       <c r="F1271" t="inlineStr"/>
-      <c r="G1271" t="b">
+      <c r="G1271" t="n">
         <v>1</v>
       </c>
       <c r="H1271" t="n">
@@ -35338,6 +35338,6882 @@
       </c>
       <c r="J1271" t="inlineStr"/>
       <c r="K1271" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="1" t="n">
+        <v>46152.39439129629</v>
+      </c>
+      <c r="B1272" t="n">
+        <v>66.735</v>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr"/>
+      <c r="E1272" t="inlineStr"/>
+      <c r="F1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1272" t="inlineStr"/>
+      <c r="H1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1272" t="inlineStr"/>
+      <c r="K1272" t="inlineStr"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="1" t="n">
+        <v>46152.39439778935</v>
+      </c>
+      <c r="B1273" t="n">
+        <v>67.29600000000001</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr"/>
+      <c r="E1273" t="inlineStr"/>
+      <c r="F1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1273" t="inlineStr"/>
+      <c r="H1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1273" t="inlineStr"/>
+      <c r="K1273" t="inlineStr"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="1" t="n">
+        <v>46152.39442</v>
+      </c>
+      <c r="B1274" t="n">
+        <v>69.215</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr"/>
+      <c r="E1274" t="inlineStr"/>
+      <c r="F1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1274" t="inlineStr"/>
+      <c r="H1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1274" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1274" t="inlineStr"/>
+      <c r="K1274" t="inlineStr"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="1" t="n">
+        <v>46152.39442447916</v>
+      </c>
+      <c r="B1275" t="n">
+        <v>69.602</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr"/>
+      <c r="E1275" t="inlineStr"/>
+      <c r="F1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1275" t="inlineStr"/>
+      <c r="H1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1275" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1275" t="inlineStr"/>
+      <c r="K1275" t="inlineStr"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="1" t="n">
+        <v>46152.39443864583</v>
+      </c>
+      <c r="B1276" t="n">
+        <v>70.82599999999999</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr"/>
+      <c r="E1276" t="inlineStr"/>
+      <c r="F1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1276" t="inlineStr"/>
+      <c r="H1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1276" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1276" t="inlineStr"/>
+      <c r="K1276" t="inlineStr"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>46152.39444418981</v>
+      </c>
+      <c r="B1277" t="n">
+        <v>71.30500000000001</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr"/>
+      <c r="E1277" t="inlineStr"/>
+      <c r="F1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1277" t="inlineStr"/>
+      <c r="H1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1277" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1277" t="inlineStr"/>
+      <c r="K1277" t="inlineStr"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="1" t="n">
+        <v>46152.39447424769</v>
+      </c>
+      <c r="B1278" t="n">
+        <v>73.902</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr"/>
+      <c r="E1278" t="inlineStr"/>
+      <c r="F1278" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1278" t="inlineStr"/>
+      <c r="H1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1278" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1278" t="inlineStr"/>
+      <c r="K1278" t="inlineStr"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="1" t="n">
+        <v>46152.39447787037</v>
+      </c>
+      <c r="B1279" t="n">
+        <v>74.215</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr"/>
+      <c r="E1279" t="inlineStr"/>
+      <c r="F1279" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1279" t="inlineStr"/>
+      <c r="H1279" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1279" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1279" t="inlineStr"/>
+      <c r="K1279" t="inlineStr"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>46152.39448542824</v>
+      </c>
+      <c r="B1280" t="n">
+        <v>74.86799999999999</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr"/>
+      <c r="E1280" t="inlineStr"/>
+      <c r="F1280" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1280" t="inlineStr"/>
+      <c r="H1280" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1280" t="n">
+        <v>9</v>
+      </c>
+      <c r="J1280" t="inlineStr"/>
+      <c r="K1280" t="inlineStr"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>46152.3944894213</v>
+      </c>
+      <c r="B1281" t="n">
+        <v>75.212</v>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr"/>
+      <c r="E1281" t="inlineStr"/>
+      <c r="F1281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1281" t="inlineStr"/>
+      <c r="H1281" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1281" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1281" t="inlineStr"/>
+      <c r="K1281" t="inlineStr"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="1" t="n">
+        <v>46152.39451625</v>
+      </c>
+      <c r="B1282" t="n">
+        <v>77.53100000000001</v>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr"/>
+      <c r="E1282" t="inlineStr"/>
+      <c r="F1282" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1282" t="inlineStr"/>
+      <c r="H1282" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1282" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1282" t="inlineStr"/>
+      <c r="K1282" t="inlineStr"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="1" t="n">
+        <v>46152.39451951389</v>
+      </c>
+      <c r="B1283" t="n">
+        <v>77.813</v>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr"/>
+      <c r="E1283" t="inlineStr"/>
+      <c r="F1283" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1283" t="inlineStr"/>
+      <c r="H1283" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1283" t="n">
+        <v>12</v>
+      </c>
+      <c r="J1283" t="inlineStr"/>
+      <c r="K1283" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="1" t="n">
+        <v>46152.39452295139</v>
+      </c>
+      <c r="B1284" t="n">
+        <v>78.11</v>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr"/>
+      <c r="E1284" t="inlineStr"/>
+      <c r="F1284" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1284" t="inlineStr"/>
+      <c r="H1284" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1284" t="n">
+        <v>13</v>
+      </c>
+      <c r="J1284" t="inlineStr"/>
+      <c r="K1284" t="inlineStr"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>46152.39452849537</v>
+      </c>
+      <c r="B1285" t="n">
+        <v>78.58799999999999</v>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr"/>
+      <c r="E1285" t="inlineStr"/>
+      <c r="F1285" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1285" t="inlineStr"/>
+      <c r="H1285" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1285" t="n">
+        <v>14</v>
+      </c>
+      <c r="J1285" t="inlineStr"/>
+      <c r="K1285" t="inlineStr"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>46152.3945350463</v>
+      </c>
+      <c r="B1286" t="n">
+        <v>79.155</v>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr"/>
+      <c r="E1286" t="inlineStr"/>
+      <c r="F1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1286" t="inlineStr"/>
+      <c r="H1286" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1286" t="n">
+        <v>15</v>
+      </c>
+      <c r="J1286" t="inlineStr"/>
+      <c r="K1286" t="inlineStr"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="1" t="n">
+        <v>46152.39454162037</v>
+      </c>
+      <c r="B1287" t="n">
+        <v>79.723</v>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr"/>
+      <c r="E1287" t="inlineStr"/>
+      <c r="F1287" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1287" t="inlineStr"/>
+      <c r="H1287" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1287" t="n">
+        <v>16</v>
+      </c>
+      <c r="J1287" t="inlineStr"/>
+      <c r="K1287" t="inlineStr"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="1" t="n">
+        <v>46152.39454866898</v>
+      </c>
+      <c r="B1288" t="n">
+        <v>80.331</v>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr"/>
+      <c r="E1288" t="inlineStr"/>
+      <c r="F1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1288" t="inlineStr"/>
+      <c r="H1288" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1288" t="n">
+        <v>17</v>
+      </c>
+      <c r="J1288" t="inlineStr"/>
+      <c r="K1288" t="inlineStr"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="1" t="n">
+        <v>46152.39455434028</v>
+      </c>
+      <c r="B1289" t="n">
+        <v>80.822</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr"/>
+      <c r="E1289" t="inlineStr"/>
+      <c r="F1289" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1289" t="inlineStr"/>
+      <c r="H1289" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1289" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1289" t="inlineStr"/>
+      <c r="K1289" t="inlineStr"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="1" t="n">
+        <v>46152.39456289352</v>
+      </c>
+      <c r="B1290" t="n">
+        <v>81.56100000000001</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr"/>
+      <c r="E1290" t="inlineStr"/>
+      <c r="F1290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1290" t="inlineStr"/>
+      <c r="H1290" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1290" t="n">
+        <v>19</v>
+      </c>
+      <c r="J1290" t="inlineStr"/>
+      <c r="K1290" t="inlineStr"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="1" t="n">
+        <v>46152.39456998843</v>
+      </c>
+      <c r="B1291" t="n">
+        <v>82.17400000000001</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr"/>
+      <c r="E1291" t="inlineStr"/>
+      <c r="F1291" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1291" t="inlineStr"/>
+      <c r="H1291" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1291" t="n">
+        <v>20</v>
+      </c>
+      <c r="J1291" t="inlineStr"/>
+      <c r="K1291" t="inlineStr"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="1" t="n">
+        <v>46152.39457662037</v>
+      </c>
+      <c r="B1292" t="n">
+        <v>82.747</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr"/>
+      <c r="E1292" t="inlineStr"/>
+      <c r="F1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1292" t="inlineStr"/>
+      <c r="H1292" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1292" t="n">
+        <v>21</v>
+      </c>
+      <c r="J1292" t="inlineStr"/>
+      <c r="K1292" t="inlineStr"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="1" t="n">
+        <v>46152.39458348379</v>
+      </c>
+      <c r="B1293" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr"/>
+      <c r="E1293" t="inlineStr"/>
+      <c r="F1293" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1293" t="inlineStr"/>
+      <c r="H1293" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1293" t="n">
+        <v>22</v>
+      </c>
+      <c r="J1293" t="inlineStr"/>
+      <c r="K1293" t="inlineStr"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="1" t="n">
+        <v>46152.39459097222</v>
+      </c>
+      <c r="B1294" t="n">
+        <v>83.98699999999999</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr"/>
+      <c r="E1294" t="inlineStr"/>
+      <c r="F1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1294" t="inlineStr"/>
+      <c r="H1294" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1294" t="n">
+        <v>23</v>
+      </c>
+      <c r="J1294" t="inlineStr"/>
+      <c r="K1294" t="inlineStr"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="1" t="n">
+        <v>46152.39460284722</v>
+      </c>
+      <c r="B1295" t="n">
+        <v>85.01300000000001</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr"/>
+      <c r="E1295" t="inlineStr"/>
+      <c r="F1295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1295" t="inlineStr"/>
+      <c r="H1295" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1295" t="n">
+        <v>24</v>
+      </c>
+      <c r="J1295" t="inlineStr"/>
+      <c r="K1295" t="inlineStr"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="1" t="n">
+        <v>46152.39461421296</v>
+      </c>
+      <c r="B1296" t="n">
+        <v>85.995</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr"/>
+      <c r="E1296" t="inlineStr"/>
+      <c r="F1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1296" t="inlineStr"/>
+      <c r="H1296" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1296" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1296" t="inlineStr"/>
+      <c r="K1296" t="inlineStr"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="1" t="n">
+        <v>46152.39463424768</v>
+      </c>
+      <c r="B1297" t="n">
+        <v>87.726</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr"/>
+      <c r="E1297" t="inlineStr"/>
+      <c r="F1297" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1297" t="inlineStr"/>
+      <c r="H1297" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1297" t="n">
+        <v>26</v>
+      </c>
+      <c r="J1297" t="inlineStr"/>
+      <c r="K1297" t="inlineStr"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="1" t="n">
+        <v>46152.39463862268</v>
+      </c>
+      <c r="B1298" t="n">
+        <v>88.104</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr"/>
+      <c r="E1298" t="inlineStr"/>
+      <c r="F1298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1298" t="inlineStr"/>
+      <c r="H1298" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1298" t="n">
+        <v>27</v>
+      </c>
+      <c r="J1298" t="inlineStr"/>
+      <c r="K1298" t="inlineStr"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="1" t="n">
+        <v>46152.39464159722</v>
+      </c>
+      <c r="B1299" t="n">
+        <v>88.361</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr"/>
+      <c r="E1299" t="inlineStr"/>
+      <c r="F1299" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1299" t="inlineStr"/>
+      <c r="H1299" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1299" t="n">
+        <v>28</v>
+      </c>
+      <c r="J1299" t="inlineStr"/>
+      <c r="K1299" t="inlineStr"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46152.39464737268</v>
+      </c>
+      <c r="B1300" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr"/>
+      <c r="E1300" t="inlineStr"/>
+      <c r="F1300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1300" t="inlineStr"/>
+      <c r="H1300" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1300" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1300" t="inlineStr"/>
+      <c r="K1300" t="inlineStr"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46152.39465840278</v>
+      </c>
+      <c r="B1301" t="n">
+        <v>89.813</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1301" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1301" t="inlineStr"/>
+      <c r="G1301" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1301" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1301" t="inlineStr"/>
+      <c r="K1301" t="inlineStr"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46152.39467195602</v>
+      </c>
+      <c r="B1302" t="n">
+        <v>90.98399999999999</v>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr"/>
+      <c r="E1302" t="inlineStr"/>
+      <c r="F1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1302" t="inlineStr"/>
+      <c r="H1302" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1302" t="n">
+        <v>30</v>
+      </c>
+      <c r="J1302" t="inlineStr"/>
+      <c r="K1302" t="inlineStr"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46152.39467690972</v>
+      </c>
+      <c r="B1303" t="n">
+        <v>91.41200000000001</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr"/>
+      <c r="E1303" t="inlineStr"/>
+      <c r="F1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1303" t="inlineStr"/>
+      <c r="H1303" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1303" t="n">
+        <v>31</v>
+      </c>
+      <c r="J1303" t="inlineStr"/>
+      <c r="K1303" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>46152.39477756945</v>
+      </c>
+      <c r="B1304" t="n">
+        <v>100.108</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr"/>
+      <c r="E1304" t="inlineStr"/>
+      <c r="F1304" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1304" t="inlineStr"/>
+      <c r="H1304" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1304" t="n">
+        <v>32</v>
+      </c>
+      <c r="J1304" t="inlineStr"/>
+      <c r="K1304" t="inlineStr"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>46152.39478078704</v>
+      </c>
+      <c r="B1305" t="n">
+        <v>100.387</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr"/>
+      <c r="E1305" t="inlineStr"/>
+      <c r="F1305" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1305" t="inlineStr"/>
+      <c r="H1305" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1305" t="n">
+        <v>33</v>
+      </c>
+      <c r="J1305" t="inlineStr"/>
+      <c r="K1305" t="inlineStr"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46152.39478331018</v>
+      </c>
+      <c r="B1306" t="n">
+        <v>100.605</v>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr"/>
+      <c r="E1306" t="inlineStr"/>
+      <c r="F1306" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1306" t="inlineStr"/>
+      <c r="H1306" t="n">
+        <v>9</v>
+      </c>
+      <c r="I1306" t="n">
+        <v>34</v>
+      </c>
+      <c r="J1306" t="inlineStr"/>
+      <c r="K1306" t="inlineStr"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46152.39478730324</v>
+      </c>
+      <c r="B1307" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr"/>
+      <c r="E1307" t="inlineStr"/>
+      <c r="F1307" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1307" t="inlineStr"/>
+      <c r="H1307" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1307" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1307" t="inlineStr"/>
+      <c r="K1307" t="inlineStr"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46152.39479456018</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>101.577</v>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr"/>
+      <c r="E1308" t="inlineStr"/>
+      <c r="F1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1308" t="inlineStr"/>
+      <c r="H1308" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1308" t="n">
+        <v>36</v>
+      </c>
+      <c r="J1308" t="inlineStr"/>
+      <c r="K1308" t="inlineStr"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46152.39479793981</v>
+      </c>
+      <c r="B1309" t="n">
+        <v>101.869</v>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr"/>
+      <c r="E1309" t="inlineStr"/>
+      <c r="F1309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1309" t="inlineStr"/>
+      <c r="H1309" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1309" t="n">
+        <v>37</v>
+      </c>
+      <c r="J1309" t="inlineStr"/>
+      <c r="K1309" t="inlineStr"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46152.39480631945</v>
+      </c>
+      <c r="B1310" t="n">
+        <v>102.593</v>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1310" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1310" t="inlineStr"/>
+      <c r="G1310" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1310" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1310" t="inlineStr"/>
+      <c r="K1310" t="inlineStr"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>46152.3948318287</v>
+      </c>
+      <c r="B1311" t="n">
+        <v>104.797</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr"/>
+      <c r="E1311" t="inlineStr"/>
+      <c r="F1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1311" t="inlineStr"/>
+      <c r="H1311" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1311" t="n">
+        <v>38</v>
+      </c>
+      <c r="J1311" t="inlineStr"/>
+      <c r="K1311" t="inlineStr"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>46152.39487984954</v>
+      </c>
+      <c r="B1312" t="n">
+        <v>108.946</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr"/>
+      <c r="E1312" t="inlineStr"/>
+      <c r="F1312" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1312" t="inlineStr"/>
+      <c r="H1312" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1312" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1312" t="inlineStr"/>
+      <c r="K1312" t="inlineStr"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46152.39488289352</v>
+      </c>
+      <c r="B1313" t="n">
+        <v>109.209</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr"/>
+      <c r="E1313" t="inlineStr"/>
+      <c r="F1313" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1313" t="inlineStr"/>
+      <c r="H1313" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1313" t="n">
+        <v>40</v>
+      </c>
+      <c r="J1313" t="inlineStr"/>
+      <c r="K1313" t="inlineStr"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46152.39491696759</v>
+      </c>
+      <c r="B1314" t="n">
+        <v>112.153</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr"/>
+      <c r="E1314" t="inlineStr"/>
+      <c r="F1314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1314" t="inlineStr"/>
+      <c r="H1314" t="n">
+        <v>12</v>
+      </c>
+      <c r="I1314" t="n">
+        <v>41</v>
+      </c>
+      <c r="J1314" t="inlineStr"/>
+      <c r="K1314" t="inlineStr"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46152.39494625</v>
+      </c>
+      <c r="B1315" t="n">
+        <v>114.683</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr"/>
+      <c r="E1315" t="inlineStr"/>
+      <c r="F1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1315" t="inlineStr"/>
+      <c r="H1315" t="n">
+        <v>13</v>
+      </c>
+      <c r="I1315" t="n">
+        <v>42</v>
+      </c>
+      <c r="J1315" t="inlineStr"/>
+      <c r="K1315" t="inlineStr"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46152.39494835648</v>
+      </c>
+      <c r="B1316" t="n">
+        <v>114.864</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr"/>
+      <c r="E1316" t="inlineStr"/>
+      <c r="F1316" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1316" t="inlineStr"/>
+      <c r="H1316" t="n">
+        <v>13</v>
+      </c>
+      <c r="I1316" t="n">
+        <v>43</v>
+      </c>
+      <c r="J1316" t="inlineStr"/>
+      <c r="K1316" t="inlineStr"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46152.39495458333</v>
+      </c>
+      <c r="B1317" t="n">
+        <v>115.403</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr"/>
+      <c r="E1317" t="inlineStr"/>
+      <c r="F1317" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1317" t="inlineStr"/>
+      <c r="H1317" t="n">
+        <v>13</v>
+      </c>
+      <c r="I1317" t="n">
+        <v>44</v>
+      </c>
+      <c r="J1317" t="inlineStr"/>
+      <c r="K1317" t="inlineStr"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46152.39498784722</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>118.277</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr"/>
+      <c r="E1318" t="inlineStr"/>
+      <c r="F1318" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1318" t="inlineStr"/>
+      <c r="H1318" t="n">
+        <v>14</v>
+      </c>
+      <c r="I1318" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1318" t="inlineStr"/>
+      <c r="K1318" t="inlineStr"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46152.39499123843</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>118.57</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr"/>
+      <c r="E1319" t="inlineStr"/>
+      <c r="F1319" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1319" t="inlineStr"/>
+      <c r="H1319" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1319" t="n">
+        <v>46</v>
+      </c>
+      <c r="J1319" t="inlineStr"/>
+      <c r="K1319" t="inlineStr"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46152.39499471064</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr"/>
+      <c r="E1320" t="inlineStr"/>
+      <c r="F1320" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1320" t="inlineStr"/>
+      <c r="H1320" t="n">
+        <v>16</v>
+      </c>
+      <c r="I1320" t="n">
+        <v>47</v>
+      </c>
+      <c r="J1320" t="inlineStr"/>
+      <c r="K1320" t="inlineStr"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46152.39499813657</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>119.165</v>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr"/>
+      <c r="E1321" t="inlineStr"/>
+      <c r="F1321" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1321" t="inlineStr"/>
+      <c r="H1321" t="n">
+        <v>17</v>
+      </c>
+      <c r="I1321" t="n">
+        <v>48</v>
+      </c>
+      <c r="J1321" t="inlineStr"/>
+      <c r="K1321" t="inlineStr"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46152.39500101852</v>
+      </c>
+      <c r="B1322" t="n">
+        <v>119.414</v>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr"/>
+      <c r="E1322" t="inlineStr"/>
+      <c r="F1322" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1322" t="inlineStr"/>
+      <c r="H1322" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1322" t="n">
+        <v>49</v>
+      </c>
+      <c r="J1322" t="inlineStr"/>
+      <c r="K1322" t="inlineStr"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46152.39503230324</v>
+      </c>
+      <c r="B1323" t="n">
+        <v>122.118</v>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr"/>
+      <c r="E1323" t="inlineStr"/>
+      <c r="F1323" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1323" t="inlineStr"/>
+      <c r="H1323" t="n">
+        <v>19</v>
+      </c>
+      <c r="I1323" t="n">
+        <v>50</v>
+      </c>
+      <c r="J1323" t="inlineStr"/>
+      <c r="K1323" t="inlineStr"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46152.39506289352</v>
+      </c>
+      <c r="B1324" t="n">
+        <v>124.761</v>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr"/>
+      <c r="E1324" t="inlineStr"/>
+      <c r="F1324" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1324" t="inlineStr"/>
+      <c r="H1324" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1324" t="n">
+        <v>51</v>
+      </c>
+      <c r="J1324" t="inlineStr"/>
+      <c r="K1324" t="inlineStr"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46152.39507417824</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>125.735</v>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr"/>
+      <c r="E1325" t="inlineStr"/>
+      <c r="F1325" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1325" t="inlineStr"/>
+      <c r="H1325" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1325" t="n">
+        <v>52</v>
+      </c>
+      <c r="J1325" t="inlineStr"/>
+      <c r="K1325" t="inlineStr"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46152.39508157408</v>
+      </c>
+      <c r="B1326" t="n">
+        <v>126.375</v>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr"/>
+      <c r="E1326" t="inlineStr"/>
+      <c r="F1326" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1326" t="inlineStr"/>
+      <c r="H1326" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1326" t="n">
+        <v>53</v>
+      </c>
+      <c r="J1326" t="inlineStr"/>
+      <c r="K1326" t="inlineStr"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46152.39509371528</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>127.424</v>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1327" t="inlineStr"/>
+      <c r="G1327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1327" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1327" t="inlineStr"/>
+      <c r="K1327" t="inlineStr"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46152.39510487269</v>
+      </c>
+      <c r="B1328" t="n">
+        <v>128.388</v>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr"/>
+      <c r="E1328" t="inlineStr"/>
+      <c r="F1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1328" t="inlineStr"/>
+      <c r="H1328" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1328" t="n">
+        <v>54</v>
+      </c>
+      <c r="J1328" t="inlineStr"/>
+      <c r="K1328" t="inlineStr"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46152.3951134375</v>
+      </c>
+      <c r="B1329" t="n">
+        <v>129.128</v>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr"/>
+      <c r="E1329" t="inlineStr"/>
+      <c r="F1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1329" t="inlineStr"/>
+      <c r="H1329" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1329" t="n">
+        <v>55</v>
+      </c>
+      <c r="J1329" t="inlineStr"/>
+      <c r="K1329" t="inlineStr"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46152.39512018519</v>
+      </c>
+      <c r="B1330" t="n">
+        <v>129.71</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr"/>
+      <c r="E1330" t="inlineStr"/>
+      <c r="F1330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1330" t="inlineStr"/>
+      <c r="H1330" t="n">
+        <v>21</v>
+      </c>
+      <c r="I1330" t="n">
+        <v>56</v>
+      </c>
+      <c r="J1330" t="inlineStr"/>
+      <c r="K1330" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46152.39521399306</v>
+      </c>
+      <c r="B1331" t="n">
+        <v>137.816</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr"/>
+      <c r="E1331" t="inlineStr"/>
+      <c r="F1331" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1331" t="inlineStr"/>
+      <c r="H1331" t="n">
+        <v>22</v>
+      </c>
+      <c r="I1331" t="n">
+        <v>57</v>
+      </c>
+      <c r="J1331" t="inlineStr"/>
+      <c r="K1331" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46152.3952172338</v>
+      </c>
+      <c r="B1332" t="n">
+        <v>138.096</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr"/>
+      <c r="E1332" t="inlineStr"/>
+      <c r="F1332" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1332" t="inlineStr"/>
+      <c r="H1332" t="n">
+        <v>22</v>
+      </c>
+      <c r="I1332" t="n">
+        <v>58</v>
+      </c>
+      <c r="J1332" t="inlineStr"/>
+      <c r="K1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46152.39522258102</v>
+      </c>
+      <c r="B1333" t="n">
+        <v>138.558</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1333" t="inlineStr"/>
+      <c r="G1333" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>23</v>
+      </c>
+      <c r="I1333" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1333" t="inlineStr"/>
+      <c r="K1333" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46152.39524770834</v>
+      </c>
+      <c r="B1334" t="n">
+        <v>140.729</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr"/>
+      <c r="E1334" t="inlineStr"/>
+      <c r="F1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1334" t="inlineStr"/>
+      <c r="H1334" t="n">
+        <v>23</v>
+      </c>
+      <c r="I1334" t="n">
+        <v>59</v>
+      </c>
+      <c r="J1334" t="inlineStr"/>
+      <c r="K1334" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46152.39525969907</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>141.765</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr"/>
+      <c r="E1335" t="inlineStr"/>
+      <c r="F1335" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1335" t="inlineStr"/>
+      <c r="H1335" t="n">
+        <v>23</v>
+      </c>
+      <c r="I1335" t="n">
+        <v>60</v>
+      </c>
+      <c r="J1335" t="inlineStr"/>
+      <c r="K1335" t="inlineStr"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46152.39531487269</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>146.532</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr"/>
+      <c r="E1336" t="inlineStr"/>
+      <c r="F1336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1336" t="inlineStr"/>
+      <c r="H1336" t="n">
+        <v>24</v>
+      </c>
+      <c r="I1336" t="n">
+        <v>61</v>
+      </c>
+      <c r="J1336" t="inlineStr"/>
+      <c r="K1336" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46152.39531811343</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>146.812</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr"/>
+      <c r="E1337" t="inlineStr"/>
+      <c r="F1337" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1337" t="inlineStr"/>
+      <c r="H1337" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1337" t="n">
+        <v>62</v>
+      </c>
+      <c r="J1337" t="inlineStr"/>
+      <c r="K1337" t="inlineStr"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46152.39534692129</v>
+      </c>
+      <c r="B1338" t="n">
+        <v>149.301</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr"/>
+      <c r="E1338" t="inlineStr"/>
+      <c r="F1338" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1338" t="inlineStr"/>
+      <c r="H1338" t="n">
+        <v>26</v>
+      </c>
+      <c r="I1338" t="n">
+        <v>63</v>
+      </c>
+      <c r="J1338" t="inlineStr"/>
+      <c r="K1338" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46152.39535013889</v>
+      </c>
+      <c r="B1339" t="n">
+        <v>149.579</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr"/>
+      <c r="E1339" t="inlineStr"/>
+      <c r="F1339" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1339" t="inlineStr"/>
+      <c r="H1339" t="n">
+        <v>27</v>
+      </c>
+      <c r="I1339" t="n">
+        <v>64</v>
+      </c>
+      <c r="J1339" t="inlineStr"/>
+      <c r="K1339" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46152.39537368056</v>
+      </c>
+      <c r="B1340" t="n">
+        <v>151.613</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr"/>
+      <c r="E1340" t="inlineStr"/>
+      <c r="F1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1340" t="inlineStr"/>
+      <c r="H1340" t="n">
+        <v>28</v>
+      </c>
+      <c r="I1340" t="n">
+        <v>65</v>
+      </c>
+      <c r="J1340" t="inlineStr"/>
+      <c r="K1340" t="inlineStr"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46152.39537581019</v>
+      </c>
+      <c r="B1341" t="n">
+        <v>151.797</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr"/>
+      <c r="E1341" t="inlineStr"/>
+      <c r="F1341" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1341" t="inlineStr"/>
+      <c r="H1341" t="n">
+        <v>28</v>
+      </c>
+      <c r="I1341" t="n">
+        <v>66</v>
+      </c>
+      <c r="J1341" t="inlineStr"/>
+      <c r="K1341" t="inlineStr"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46152.39542806713</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>156.312</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr"/>
+      <c r="E1342" t="inlineStr"/>
+      <c r="F1342" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1342" t="inlineStr"/>
+      <c r="H1342" t="n">
+        <v>28</v>
+      </c>
+      <c r="I1342" t="n">
+        <v>67</v>
+      </c>
+      <c r="J1342" t="inlineStr"/>
+      <c r="K1342" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46152.39547832176</v>
+      </c>
+      <c r="B1343" t="n">
+        <v>160.654</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr"/>
+      <c r="E1343" t="inlineStr"/>
+      <c r="F1343" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1343" t="inlineStr"/>
+      <c r="H1343" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1343" t="n">
+        <v>68</v>
+      </c>
+      <c r="J1343" t="inlineStr"/>
+      <c r="K1343" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>46152.39548525463</v>
+      </c>
+      <c r="B1344" t="n">
+        <v>161.253</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr"/>
+      <c r="E1344" t="inlineStr"/>
+      <c r="F1344" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1344" t="inlineStr"/>
+      <c r="H1344" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1344" t="n">
+        <v>69</v>
+      </c>
+      <c r="J1344" t="inlineStr"/>
+      <c r="K1344" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>46152.39549634259</v>
+      </c>
+      <c r="B1345" t="n">
+        <v>162.211</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1345" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1345" t="inlineStr"/>
+      <c r="G1345" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1345" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1345" t="inlineStr"/>
+      <c r="K1345" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46152.3955078588</v>
+      </c>
+      <c r="B1346" t="n">
+        <v>163.206</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr"/>
+      <c r="E1346" t="inlineStr"/>
+      <c r="F1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1346" t="inlineStr"/>
+      <c r="H1346" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1346" t="n">
+        <v>70</v>
+      </c>
+      <c r="J1346" t="inlineStr"/>
+      <c r="K1346" t="inlineStr"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="1" t="n">
+        <v>46152.39551972222</v>
+      </c>
+      <c r="B1347" t="n">
+        <v>164.231</v>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr"/>
+      <c r="E1347" t="inlineStr"/>
+      <c r="F1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1347" t="inlineStr"/>
+      <c r="H1347" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1347" t="n">
+        <v>71</v>
+      </c>
+      <c r="J1347" t="inlineStr"/>
+      <c r="K1347" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>46152.3955262963</v>
+      </c>
+      <c r="B1348" t="n">
+        <v>164.799</v>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr"/>
+      <c r="E1348" t="inlineStr"/>
+      <c r="F1348" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1348" t="n">
+        <v>72</v>
+      </c>
+      <c r="J1348" t="inlineStr"/>
+      <c r="K1348" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>46152.39555564815</v>
+      </c>
+      <c r="B1349" t="n">
+        <v>167.335</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr"/>
+      <c r="E1349" t="inlineStr"/>
+      <c r="F1349" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1349" t="n">
+        <v>73</v>
+      </c>
+      <c r="J1349" t="inlineStr"/>
+      <c r="K1349" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46152.39555924769</v>
+      </c>
+      <c r="B1350" t="n">
+        <v>167.646</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr"/>
+      <c r="E1350" t="inlineStr"/>
+      <c r="F1350" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1350" t="inlineStr"/>
+      <c r="H1350" t="n">
+        <v>31</v>
+      </c>
+      <c r="I1350" t="n">
+        <v>74</v>
+      </c>
+      <c r="J1350" t="inlineStr"/>
+      <c r="K1350" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46152.39556282407</v>
+      </c>
+      <c r="B1351" t="n">
+        <v>167.955</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr"/>
+      <c r="E1351" t="inlineStr"/>
+      <c r="F1351" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1351" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1351" t="inlineStr"/>
+      <c r="K1351" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46152.39561672453</v>
+      </c>
+      <c r="B1352" t="n">
+        <v>172.612</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr"/>
+      <c r="E1352" t="inlineStr"/>
+      <c r="F1352" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="n">
+        <v>33</v>
+      </c>
+      <c r="I1352" t="n">
+        <v>76</v>
+      </c>
+      <c r="J1352" t="inlineStr"/>
+      <c r="K1352" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46152.39562097222</v>
+      </c>
+      <c r="B1353" t="n">
+        <v>172.979</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr"/>
+      <c r="E1353" t="inlineStr"/>
+      <c r="F1353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1353" t="n">
+        <v>77</v>
+      </c>
+      <c r="J1353" t="inlineStr"/>
+      <c r="K1353" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46152.39563239583</v>
+      </c>
+      <c r="B1354" t="n">
+        <v>173.966</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1354" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1354" t="inlineStr"/>
+      <c r="G1354" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1354" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1354" t="inlineStr"/>
+      <c r="K1354" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>46152.39566744213</v>
+      </c>
+      <c r="B1355" t="n">
+        <v>176.994</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr"/>
+      <c r="E1355" t="inlineStr"/>
+      <c r="F1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1355" t="n">
+        <v>78</v>
+      </c>
+      <c r="J1355" t="inlineStr"/>
+      <c r="K1355" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46152.39567974537</v>
+      </c>
+      <c r="B1356" t="n">
+        <v>178.057</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr"/>
+      <c r="E1356" t="inlineStr"/>
+      <c r="F1356" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1356" t="n">
+        <v>79</v>
+      </c>
+      <c r="J1356" t="inlineStr"/>
+      <c r="K1356" t="inlineStr"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46152.39568460648</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>178.477</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr"/>
+      <c r="E1357" t="inlineStr"/>
+      <c r="F1357" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1357" t="n">
+        <v>80</v>
+      </c>
+      <c r="J1357" t="inlineStr"/>
+      <c r="K1357" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46152.39570969907</v>
+      </c>
+      <c r="B1358" t="n">
+        <v>180.645</v>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr"/>
+      <c r="E1358" t="inlineStr"/>
+      <c r="F1358" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1358" t="n">
+        <v>81</v>
+      </c>
+      <c r="J1358" t="inlineStr"/>
+      <c r="K1358" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46152.39572723379</v>
+      </c>
+      <c r="B1359" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr"/>
+      <c r="E1359" t="inlineStr"/>
+      <c r="F1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1359" t="n">
+        <v>82</v>
+      </c>
+      <c r="J1359" t="inlineStr"/>
+      <c r="K1359" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46152.39573204861</v>
+      </c>
+      <c r="B1360" t="n">
+        <v>182.576</v>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr"/>
+      <c r="E1360" t="inlineStr"/>
+      <c r="F1360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1360" t="n">
+        <v>83</v>
+      </c>
+      <c r="J1360" t="inlineStr"/>
+      <c r="K1360" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46152.39575630787</v>
+      </c>
+      <c r="B1361" t="n">
+        <v>184.672</v>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr"/>
+      <c r="E1361" t="inlineStr"/>
+      <c r="F1361" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="n">
+        <v>37</v>
+      </c>
+      <c r="I1361" t="n">
+        <v>84</v>
+      </c>
+      <c r="J1361" t="inlineStr"/>
+      <c r="K1361" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46152.39580018519</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>188.463</v>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr"/>
+      <c r="E1362" t="inlineStr"/>
+      <c r="F1362" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="n">
+        <v>38</v>
+      </c>
+      <c r="I1362" t="n">
+        <v>85</v>
+      </c>
+      <c r="J1362" t="inlineStr"/>
+      <c r="K1362" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46152.39581962963</v>
+      </c>
+      <c r="B1363" t="n">
+        <v>190.143</v>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr"/>
+      <c r="E1363" t="inlineStr"/>
+      <c r="F1363" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1363" t="n">
+        <v>86</v>
+      </c>
+      <c r="J1363" t="inlineStr"/>
+      <c r="K1363" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46152.39582583334</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>190.679</v>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr"/>
+      <c r="E1364" t="inlineStr"/>
+      <c r="F1364" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1364" t="n">
+        <v>87</v>
+      </c>
+      <c r="J1364" t="inlineStr"/>
+      <c r="K1364" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46152.39583141204</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>191.161</v>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1365" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1365" t="inlineStr"/>
+      <c r="G1365" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1365" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1365" t="inlineStr"/>
+      <c r="K1365" t="inlineStr"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46152.39584559028</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>192.385</v>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr"/>
+      <c r="E1366" t="inlineStr"/>
+      <c r="F1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1366" t="n">
+        <v>88</v>
+      </c>
+      <c r="J1366" t="inlineStr"/>
+      <c r="K1366" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46152.39585232639</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>192.968</v>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr"/>
+      <c r="E1367" t="inlineStr"/>
+      <c r="F1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1367" t="n">
+        <v>89</v>
+      </c>
+      <c r="J1367" t="inlineStr"/>
+      <c r="K1367" t="inlineStr"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46152.3958590162</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>193.546</v>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr"/>
+      <c r="E1368" t="inlineStr"/>
+      <c r="F1368" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="n">
+        <v>39</v>
+      </c>
+      <c r="I1368" t="n">
+        <v>90</v>
+      </c>
+      <c r="J1368" t="inlineStr"/>
+      <c r="K1368" t="inlineStr"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46152.39588203704</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>195.535</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr"/>
+      <c r="E1369" t="inlineStr"/>
+      <c r="F1369" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="n">
+        <v>40</v>
+      </c>
+      <c r="I1369" t="n">
+        <v>91</v>
+      </c>
+      <c r="J1369" t="inlineStr"/>
+      <c r="K1369" t="inlineStr"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46152.39588549769</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>195.833</v>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr"/>
+      <c r="E1370" t="inlineStr"/>
+      <c r="F1370" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="n">
+        <v>41</v>
+      </c>
+      <c r="I1370" t="n">
+        <v>92</v>
+      </c>
+      <c r="J1370" t="inlineStr"/>
+      <c r="K1370" t="inlineStr"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46152.39588871528</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>196.112</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr"/>
+      <c r="E1371" t="inlineStr"/>
+      <c r="F1371" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1371" t="inlineStr"/>
+      <c r="H1371" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1371" t="n">
+        <v>93</v>
+      </c>
+      <c r="J1371" t="inlineStr"/>
+      <c r="K1371" t="inlineStr"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46152.39589200231</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>196.396</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr"/>
+      <c r="E1372" t="inlineStr"/>
+      <c r="F1372" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1372" t="inlineStr"/>
+      <c r="H1372" t="n">
+        <v>43</v>
+      </c>
+      <c r="I1372" t="n">
+        <v>94</v>
+      </c>
+      <c r="J1372" t="inlineStr"/>
+      <c r="K1372" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46152.39589510416</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>196.664</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr"/>
+      <c r="E1373" t="inlineStr"/>
+      <c r="F1373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="n">
+        <v>44</v>
+      </c>
+      <c r="I1373" t="n">
+        <v>95</v>
+      </c>
+      <c r="J1373" t="inlineStr"/>
+      <c r="K1373" t="inlineStr"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46152.39589819445</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>196.931</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr"/>
+      <c r="E1374" t="inlineStr"/>
+      <c r="F1374" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1374" t="n">
+        <v>96</v>
+      </c>
+      <c r="J1374" t="inlineStr"/>
+      <c r="K1374" t="inlineStr"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>46152.39590141203</v>
+      </c>
+      <c r="B1375" t="n">
+        <v>197.209</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr"/>
+      <c r="E1375" t="inlineStr"/>
+      <c r="F1375" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1375" t="n">
+        <v>97</v>
+      </c>
+      <c r="J1375" t="inlineStr"/>
+      <c r="K1375" t="inlineStr"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>46152.39590481482</v>
+      </c>
+      <c r="B1376" t="n">
+        <v>197.503</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr"/>
+      <c r="E1376" t="inlineStr"/>
+      <c r="F1376" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="n">
+        <v>47</v>
+      </c>
+      <c r="I1376" t="n">
+        <v>98</v>
+      </c>
+      <c r="J1376" t="inlineStr"/>
+      <c r="K1376" t="inlineStr"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46152.39590804398</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>197.782</v>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr"/>
+      <c r="E1377" t="inlineStr"/>
+      <c r="F1377" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1377" t="inlineStr"/>
+      <c r="H1377" t="n">
+        <v>48</v>
+      </c>
+      <c r="I1377" t="n">
+        <v>99</v>
+      </c>
+      <c r="J1377" t="inlineStr"/>
+      <c r="K1377" t="inlineStr"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46152.39593405092</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>200.029</v>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr"/>
+      <c r="E1378" t="inlineStr"/>
+      <c r="F1378" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1378" t="inlineStr"/>
+      <c r="H1378" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1378" t="n">
+        <v>100</v>
+      </c>
+      <c r="J1378" t="inlineStr"/>
+      <c r="K1378" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46152.39593979167</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>200.525</v>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr"/>
+      <c r="E1379" t="inlineStr"/>
+      <c r="F1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1379" t="inlineStr"/>
+      <c r="H1379" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1379" t="n">
+        <v>101</v>
+      </c>
+      <c r="J1379" t="inlineStr"/>
+      <c r="K1379" t="inlineStr"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="1" t="n">
+        <v>46152.39594346065</v>
+      </c>
+      <c r="B1380" t="n">
+        <v>200.842</v>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr"/>
+      <c r="E1380" t="inlineStr"/>
+      <c r="F1380" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1380" t="inlineStr"/>
+      <c r="H1380" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1380" t="n">
+        <v>102</v>
+      </c>
+      <c r="J1380" t="inlineStr"/>
+      <c r="K1380" t="inlineStr"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="1" t="n">
+        <v>46152.39595446759</v>
+      </c>
+      <c r="B1381" t="n">
+        <v>201.793</v>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1381" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1381" t="inlineStr"/>
+      <c r="G1381" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1381" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1381" t="inlineStr"/>
+      <c r="K1381" t="inlineStr"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="1" t="n">
+        <v>46152.39597512731</v>
+      </c>
+      <c r="B1382" t="n">
+        <v>203.578</v>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr"/>
+      <c r="E1382" t="inlineStr"/>
+      <c r="F1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1382" t="inlineStr"/>
+      <c r="H1382" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1382" t="n">
+        <v>103</v>
+      </c>
+      <c r="J1382" t="inlineStr"/>
+      <c r="K1382" t="inlineStr"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="1" t="n">
+        <v>46152.39601068287</v>
+      </c>
+      <c r="B1383" t="n">
+        <v>206.65</v>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr"/>
+      <c r="E1383" t="inlineStr"/>
+      <c r="F1383" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1383" t="inlineStr"/>
+      <c r="H1383" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1383" t="n">
+        <v>104</v>
+      </c>
+      <c r="J1383" t="inlineStr"/>
+      <c r="K1383" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="1" t="n">
+        <v>46152.39603798611</v>
+      </c>
+      <c r="B1384" t="n">
+        <v>209.009</v>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr"/>
+      <c r="E1384" t="inlineStr"/>
+      <c r="F1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1384" t="inlineStr"/>
+      <c r="H1384" t="n">
+        <v>50</v>
+      </c>
+      <c r="I1384" t="n">
+        <v>105</v>
+      </c>
+      <c r="J1384" t="inlineStr"/>
+      <c r="K1384" t="inlineStr"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="1" t="n">
+        <v>46152.39604366898</v>
+      </c>
+      <c r="B1385" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr"/>
+      <c r="E1385" t="inlineStr"/>
+      <c r="F1385" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1385" t="inlineStr"/>
+      <c r="H1385" t="n">
+        <v>50</v>
+      </c>
+      <c r="I1385" t="n">
+        <v>106</v>
+      </c>
+      <c r="J1385" t="inlineStr"/>
+      <c r="K1385" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="1" t="n">
+        <v>46152.39604944445</v>
+      </c>
+      <c r="B1386" t="n">
+        <v>209.999</v>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr"/>
+      <c r="E1386" t="inlineStr"/>
+      <c r="F1386" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1386" t="inlineStr"/>
+      <c r="H1386" t="n">
+        <v>50</v>
+      </c>
+      <c r="I1386" t="n">
+        <v>107</v>
+      </c>
+      <c r="J1386" t="inlineStr"/>
+      <c r="K1386" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="1" t="n">
+        <v>46152.39606876158</v>
+      </c>
+      <c r="B1387" t="n">
+        <v>211.668</v>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr"/>
+      <c r="E1387" t="inlineStr"/>
+      <c r="F1387" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1387" t="inlineStr"/>
+      <c r="H1387" t="n">
+        <v>51</v>
+      </c>
+      <c r="I1387" t="n">
+        <v>108</v>
+      </c>
+      <c r="J1387" t="inlineStr"/>
+      <c r="K1387" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="1" t="n">
+        <v>46152.39610096065</v>
+      </c>
+      <c r="B1388" t="n">
+        <v>214.45</v>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr"/>
+      <c r="E1388" t="inlineStr"/>
+      <c r="F1388" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1388" t="inlineStr"/>
+      <c r="H1388" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1388" t="n">
+        <v>109</v>
+      </c>
+      <c r="J1388" t="inlineStr"/>
+      <c r="K1388" t="inlineStr"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="1" t="n">
+        <v>46152.39610700231</v>
+      </c>
+      <c r="B1389" t="n">
+        <v>214.972</v>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr"/>
+      <c r="E1389" t="inlineStr"/>
+      <c r="F1389" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1389" t="inlineStr"/>
+      <c r="H1389" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1389" t="n">
+        <v>110</v>
+      </c>
+      <c r="J1389" t="inlineStr"/>
+      <c r="K1389" t="inlineStr"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="1" t="n">
+        <v>46152.39611817129</v>
+      </c>
+      <c r="B1390" t="n">
+        <v>215.936</v>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1390" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1390" t="inlineStr"/>
+      <c r="G1390" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1390" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1390" t="inlineStr"/>
+      <c r="K1390" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="1" t="n">
+        <v>46152.3961328588</v>
+      </c>
+      <c r="B1391" t="n">
+        <v>217.206</v>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr"/>
+      <c r="E1391" t="inlineStr"/>
+      <c r="F1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1391" t="inlineStr"/>
+      <c r="H1391" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1391" t="n">
+        <v>111</v>
+      </c>
+      <c r="J1391" t="inlineStr"/>
+      <c r="K1391" t="inlineStr"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="1" t="n">
+        <v>46152.39613865741</v>
+      </c>
+      <c r="B1392" t="n">
+        <v>217.707</v>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr"/>
+      <c r="E1392" t="inlineStr"/>
+      <c r="F1392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1392" t="inlineStr"/>
+      <c r="H1392" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1392" t="n">
+        <v>112</v>
+      </c>
+      <c r="J1392" t="inlineStr"/>
+      <c r="K1392" t="inlineStr"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="1" t="n">
+        <v>46152.39614443287</v>
+      </c>
+      <c r="B1393" t="n">
+        <v>218.206</v>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr"/>
+      <c r="E1393" t="inlineStr"/>
+      <c r="F1393" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1393" t="n">
+        <v>113</v>
+      </c>
+      <c r="J1393" t="inlineStr"/>
+      <c r="K1393" t="inlineStr"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="1" t="n">
+        <v>46152.39614878472</v>
+      </c>
+      <c r="B1394" t="n">
+        <v>218.582</v>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr"/>
+      <c r="E1394" t="inlineStr"/>
+      <c r="F1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1394" t="inlineStr"/>
+      <c r="H1394" t="n">
+        <v>53</v>
+      </c>
+      <c r="I1394" t="n">
+        <v>114</v>
+      </c>
+      <c r="J1394" t="inlineStr"/>
+      <c r="K1394" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="1" t="n">
+        <v>46152.39615263889</v>
+      </c>
+      <c r="B1395" t="n">
+        <v>218.915</v>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr"/>
+      <c r="E1395" t="inlineStr"/>
+      <c r="F1395" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1395" t="inlineStr"/>
+      <c r="H1395" t="n">
+        <v>54</v>
+      </c>
+      <c r="I1395" t="n">
+        <v>115</v>
+      </c>
+      <c r="J1395" t="inlineStr"/>
+      <c r="K1395" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="1" t="n">
+        <v>46152.39618354166</v>
+      </c>
+      <c r="B1396" t="n">
+        <v>221.585</v>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr"/>
+      <c r="E1396" t="inlineStr"/>
+      <c r="F1396" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1396" t="inlineStr"/>
+      <c r="H1396" t="n">
+        <v>55</v>
+      </c>
+      <c r="I1396" t="n">
+        <v>116</v>
+      </c>
+      <c r="J1396" t="inlineStr"/>
+      <c r="K1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="1" t="n">
+        <v>46152.39618601852</v>
+      </c>
+      <c r="B1397" t="n">
+        <v>221.799</v>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr"/>
+      <c r="E1397" t="inlineStr"/>
+      <c r="F1397" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1397" t="n">
+        <v>117</v>
+      </c>
+      <c r="J1397" t="inlineStr"/>
+      <c r="K1397" t="inlineStr"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="1" t="n">
+        <v>46152.39620311343</v>
+      </c>
+      <c r="B1398" t="n">
+        <v>223.275</v>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr"/>
+      <c r="E1398" t="inlineStr"/>
+      <c r="F1398" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="n">
+        <v>55</v>
+      </c>
+      <c r="I1398" t="n">
+        <v>118</v>
+      </c>
+      <c r="J1398" t="inlineStr"/>
+      <c r="K1398" t="inlineStr"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="1" t="n">
+        <v>46152.39621663195</v>
+      </c>
+      <c r="B1399" t="n">
+        <v>224.443</v>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr"/>
+      <c r="E1399" t="inlineStr"/>
+      <c r="F1399" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1399" t="inlineStr"/>
+      <c r="H1399" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1399" t="n">
+        <v>119</v>
+      </c>
+      <c r="J1399" t="inlineStr"/>
+      <c r="K1399" t="inlineStr"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="1" t="n">
+        <v>46152.39623076389</v>
+      </c>
+      <c r="B1400" t="n">
+        <v>225.665</v>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1400" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1400" t="inlineStr"/>
+      <c r="G1400" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1400" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1400" t="inlineStr"/>
+      <c r="K1400" t="inlineStr"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="1" t="n">
+        <v>46152.39625299769</v>
+      </c>
+      <c r="B1401" t="n">
+        <v>227.586</v>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr"/>
+      <c r="E1401" t="inlineStr"/>
+      <c r="F1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1401" t="inlineStr"/>
+      <c r="H1401" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1401" t="n">
+        <v>120</v>
+      </c>
+      <c r="J1401" t="inlineStr"/>
+      <c r="K1401" t="inlineStr"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="1" t="n">
+        <v>46152.39630883102</v>
+      </c>
+      <c r="B1402" t="n">
+        <v>232.409</v>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr"/>
+      <c r="E1402" t="inlineStr"/>
+      <c r="F1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1402" t="inlineStr"/>
+      <c r="H1402" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1402" t="n">
+        <v>121</v>
+      </c>
+      <c r="J1402" t="inlineStr"/>
+      <c r="K1402" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="1" t="n">
+        <v>46152.39631325231</v>
+      </c>
+      <c r="B1403" t="n">
+        <v>232.792</v>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr"/>
+      <c r="E1403" t="inlineStr"/>
+      <c r="F1403" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1403" t="inlineStr"/>
+      <c r="H1403" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1403" t="n">
+        <v>122</v>
+      </c>
+      <c r="J1403" t="inlineStr"/>
+      <c r="K1403" t="inlineStr"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="1" t="n">
+        <v>46152.3963187037</v>
+      </c>
+      <c r="B1404" t="n">
+        <v>233.263</v>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr"/>
+      <c r="E1404" t="inlineStr"/>
+      <c r="F1404" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1404" t="inlineStr"/>
+      <c r="H1404" t="n">
+        <v>56</v>
+      </c>
+      <c r="I1404" t="n">
+        <v>123</v>
+      </c>
+      <c r="J1404" t="inlineStr"/>
+      <c r="K1404" t="inlineStr"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="1" t="n">
+        <v>46152.39633546296</v>
+      </c>
+      <c r="B1405" t="n">
+        <v>234.711</v>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr"/>
+      <c r="E1405" t="inlineStr"/>
+      <c r="F1405" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1405" t="inlineStr"/>
+      <c r="H1405" t="n">
+        <v>57</v>
+      </c>
+      <c r="I1405" t="n">
+        <v>124</v>
+      </c>
+      <c r="J1405" t="inlineStr"/>
+      <c r="K1405" t="inlineStr"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="1" t="n">
+        <v>46152.39635129629</v>
+      </c>
+      <c r="B1406" t="n">
+        <v>236.079</v>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr"/>
+      <c r="E1406" t="inlineStr"/>
+      <c r="F1406" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1406" t="inlineStr"/>
+      <c r="H1406" t="n">
+        <v>58</v>
+      </c>
+      <c r="I1406" t="n">
+        <v>125</v>
+      </c>
+      <c r="J1406" t="inlineStr"/>
+      <c r="K1406" t="inlineStr"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="1" t="n">
+        <v>46152.39636226852</v>
+      </c>
+      <c r="B1407" t="n">
+        <v>237.027</v>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr"/>
+      <c r="E1407" t="inlineStr"/>
+      <c r="F1407" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1407" t="inlineStr"/>
+      <c r="H1407" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1407" t="n">
+        <v>126</v>
+      </c>
+      <c r="J1407" t="inlineStr"/>
+      <c r="K1407" t="inlineStr"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="1" t="n">
+        <v>46152.39636790509</v>
+      </c>
+      <c r="B1408" t="n">
+        <v>237.514</v>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr"/>
+      <c r="E1408" t="inlineStr"/>
+      <c r="F1408" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1408" t="inlineStr"/>
+      <c r="H1408" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1408" t="n">
+        <v>127</v>
+      </c>
+      <c r="J1408" t="inlineStr"/>
+      <c r="K1408" t="inlineStr"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="1" t="n">
+        <v>46152.39637944444</v>
+      </c>
+      <c r="B1409" t="n">
+        <v>238.511</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1409" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1409" t="inlineStr"/>
+      <c r="G1409" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1409" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1409" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1409" t="inlineStr"/>
+      <c r="K1409" t="inlineStr"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="1" t="n">
+        <v>46152.39639134259</v>
+      </c>
+      <c r="B1410" t="n">
+        <v>239.539</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr"/>
+      <c r="E1410" t="inlineStr"/>
+      <c r="F1410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1410" t="inlineStr"/>
+      <c r="H1410" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1410" t="n">
+        <v>128</v>
+      </c>
+      <c r="J1410" t="inlineStr"/>
+      <c r="K1410" t="inlineStr"/>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="1" t="n">
+        <v>46152.39639622685</v>
+      </c>
+      <c r="B1411" t="n">
+        <v>239.961</v>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr"/>
+      <c r="E1411" t="inlineStr"/>
+      <c r="F1411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1411" t="inlineStr"/>
+      <c r="H1411" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1411" t="n">
+        <v>129</v>
+      </c>
+      <c r="J1411" t="inlineStr"/>
+      <c r="K1411" t="inlineStr"/>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="1" t="n">
+        <v>46152.39640246527</v>
+      </c>
+      <c r="B1412" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr"/>
+      <c r="E1412" t="inlineStr"/>
+      <c r="F1412" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1412" t="inlineStr"/>
+      <c r="H1412" t="n">
+        <v>59</v>
+      </c>
+      <c r="I1412" t="n">
+        <v>130</v>
+      </c>
+      <c r="J1412" t="inlineStr"/>
+      <c r="K1412" t="inlineStr"/>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="1" t="n">
+        <v>46152.39640596065</v>
+      </c>
+      <c r="B1413" t="n">
+        <v>240.802</v>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr"/>
+      <c r="E1413" t="inlineStr"/>
+      <c r="F1413" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1413" t="inlineStr"/>
+      <c r="H1413" t="n">
+        <v>60</v>
+      </c>
+      <c r="I1413" t="n">
+        <v>131</v>
+      </c>
+      <c r="J1413" t="inlineStr"/>
+      <c r="K1413" t="inlineStr"/>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="1" t="n">
+        <v>46152.3964696875</v>
+      </c>
+      <c r="B1414" t="n">
+        <v>246.308</v>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr"/>
+      <c r="E1414" t="inlineStr"/>
+      <c r="F1414" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1414" t="inlineStr"/>
+      <c r="H1414" t="n">
+        <v>61</v>
+      </c>
+      <c r="I1414" t="n">
+        <v>132</v>
+      </c>
+      <c r="J1414" t="inlineStr"/>
+      <c r="K1414" t="inlineStr"/>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="1" t="n">
+        <v>46152.39648361111</v>
+      </c>
+      <c r="B1415" t="n">
+        <v>247.511</v>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr"/>
+      <c r="E1415" t="inlineStr"/>
+      <c r="F1415" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1415" t="inlineStr"/>
+      <c r="H1415" t="n">
+        <v>62</v>
+      </c>
+      <c r="I1415" t="n">
+        <v>133</v>
+      </c>
+      <c r="J1415" t="inlineStr"/>
+      <c r="K1415" t="inlineStr"/>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="1" t="n">
+        <v>46152.39649836806</v>
+      </c>
+      <c r="B1416" t="n">
+        <v>248.786</v>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1416" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1416" t="inlineStr"/>
+      <c r="G1416" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>62</v>
+      </c>
+      <c r="I1416" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1416" t="inlineStr"/>
+      <c r="K1416" t="inlineStr"/>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="1" t="n">
+        <v>46152.39652506945</v>
+      </c>
+      <c r="B1417" t="n">
+        <v>251.093</v>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr"/>
+      <c r="E1417" t="inlineStr"/>
+      <c r="F1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1417" t="inlineStr"/>
+      <c r="H1417" t="n">
+        <v>62</v>
+      </c>
+      <c r="I1417" t="n">
+        <v>134</v>
+      </c>
+      <c r="J1417" t="inlineStr"/>
+      <c r="K1417" t="inlineStr"/>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="1" t="n">
+        <v>46152.39653733796</v>
+      </c>
+      <c r="B1418" t="n">
+        <v>252.153</v>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr"/>
+      <c r="E1418" t="inlineStr"/>
+      <c r="F1418" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1418" t="inlineStr"/>
+      <c r="H1418" t="n">
+        <v>62</v>
+      </c>
+      <c r="I1418" t="n">
+        <v>135</v>
+      </c>
+      <c r="J1418" t="inlineStr"/>
+      <c r="K1418" t="inlineStr"/>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="1" t="n">
+        <v>46152.39654214121</v>
+      </c>
+      <c r="B1419" t="n">
+        <v>252.568</v>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr"/>
+      <c r="E1419" t="inlineStr"/>
+      <c r="F1419" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1419" t="inlineStr"/>
+      <c r="H1419" t="n">
+        <v>63</v>
+      </c>
+      <c r="I1419" t="n">
+        <v>136</v>
+      </c>
+      <c r="J1419" t="inlineStr"/>
+      <c r="K1419" t="inlineStr"/>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="1" t="n">
+        <v>46152.39654728009</v>
+      </c>
+      <c r="B1420" t="n">
+        <v>253.012</v>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr"/>
+      <c r="E1420" t="inlineStr"/>
+      <c r="F1420" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1420" t="inlineStr"/>
+      <c r="H1420" t="n">
+        <v>64</v>
+      </c>
+      <c r="I1420" t="n">
+        <v>137</v>
+      </c>
+      <c r="J1420" t="inlineStr"/>
+      <c r="K1420" t="inlineStr"/>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="1" t="n">
+        <v>46152.39656755787</v>
+      </c>
+      <c r="B1421" t="n">
+        <v>254.764</v>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr"/>
+      <c r="E1421" t="inlineStr"/>
+      <c r="F1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1421" t="inlineStr"/>
+      <c r="H1421" t="n">
+        <v>65</v>
+      </c>
+      <c r="I1421" t="n">
+        <v>138</v>
+      </c>
+      <c r="J1421" t="inlineStr"/>
+      <c r="K1421" t="inlineStr"/>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="1" t="n">
+        <v>46152.39657277778</v>
+      </c>
+      <c r="B1422" t="n">
+        <v>255.215</v>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr"/>
+      <c r="E1422" t="inlineStr"/>
+      <c r="F1422" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1422" t="inlineStr"/>
+      <c r="H1422" t="n">
+        <v>65</v>
+      </c>
+      <c r="I1422" t="n">
+        <v>139</v>
+      </c>
+      <c r="J1422" t="inlineStr"/>
+      <c r="K1422" t="inlineStr"/>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="1" t="n">
+        <v>46152.39657842593</v>
+      </c>
+      <c r="B1423" t="n">
+        <v>255.703</v>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr"/>
+      <c r="E1423" t="inlineStr"/>
+      <c r="F1423" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1423" t="inlineStr"/>
+      <c r="H1423" t="n">
+        <v>65</v>
+      </c>
+      <c r="I1423" t="n">
+        <v>140</v>
+      </c>
+      <c r="J1423" t="inlineStr"/>
+      <c r="K1423" t="inlineStr"/>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="1" t="n">
+        <v>46152.39658206019</v>
+      </c>
+      <c r="B1424" t="n">
+        <v>256.017</v>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr"/>
+      <c r="E1424" t="inlineStr"/>
+      <c r="F1424" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1424" t="inlineStr"/>
+      <c r="H1424" t="n">
+        <v>66</v>
+      </c>
+      <c r="I1424" t="n">
+        <v>141</v>
+      </c>
+      <c r="J1424" t="inlineStr"/>
+      <c r="K1424" t="inlineStr"/>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="1" t="n">
+        <v>46152.39659738426</v>
+      </c>
+      <c r="B1425" t="n">
+        <v>257.341</v>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr"/>
+      <c r="E1425" t="inlineStr"/>
+      <c r="F1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1425" t="inlineStr"/>
+      <c r="H1425" t="n">
+        <v>67</v>
+      </c>
+      <c r="I1425" t="n">
+        <v>142</v>
+      </c>
+      <c r="J1425" t="inlineStr"/>
+      <c r="K1425" t="inlineStr"/>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="1" t="n">
+        <v>46152.39660766203</v>
+      </c>
+      <c r="B1426" t="n">
+        <v>258.229</v>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr"/>
+      <c r="E1426" t="inlineStr"/>
+      <c r="F1426" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1426" t="inlineStr"/>
+      <c r="H1426" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1426" t="n">
+        <v>143</v>
+      </c>
+      <c r="J1426" t="inlineStr"/>
+      <c r="K1426" t="inlineStr"/>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="1" t="n">
+        <v>46152.39661248842</v>
+      </c>
+      <c r="B1427" t="n">
+        <v>258.646</v>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr"/>
+      <c r="E1427" t="inlineStr"/>
+      <c r="F1427" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1427" t="inlineStr"/>
+      <c r="H1427" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1427" t="n">
+        <v>144</v>
+      </c>
+      <c r="J1427" t="inlineStr"/>
+      <c r="K1427" t="inlineStr"/>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="1" t="n">
+        <v>46152.39662697916</v>
+      </c>
+      <c r="B1428" t="n">
+        <v>259.898</v>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1428" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1428" t="inlineStr"/>
+      <c r="G1428" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1428" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1428" t="inlineStr"/>
+      <c r="K1428" t="inlineStr"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="1" t="n">
+        <v>46152.39664144676</v>
+      </c>
+      <c r="B1429" t="n">
+        <v>261.148</v>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr"/>
+      <c r="E1429" t="inlineStr"/>
+      <c r="F1429" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1429" t="inlineStr"/>
+      <c r="H1429" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1429" t="n">
+        <v>145</v>
+      </c>
+      <c r="J1429" t="inlineStr"/>
+      <c r="K1429" t="inlineStr"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="1" t="n">
+        <v>46152.39664537037</v>
+      </c>
+      <c r="B1430" t="n">
+        <v>261.486</v>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr"/>
+      <c r="E1430" t="inlineStr"/>
+      <c r="F1430" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1430" t="inlineStr"/>
+      <c r="H1430" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1430" t="n">
+        <v>146</v>
+      </c>
+      <c r="J1430" t="inlineStr"/>
+      <c r="K1430" t="inlineStr"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="1" t="n">
+        <v>46152.39665096065</v>
+      </c>
+      <c r="B1431" t="n">
+        <v>261.97</v>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr"/>
+      <c r="E1431" t="inlineStr"/>
+      <c r="F1431" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1431" t="inlineStr"/>
+      <c r="H1431" t="n">
+        <v>68</v>
+      </c>
+      <c r="I1431" t="n">
+        <v>147</v>
+      </c>
+      <c r="J1431" t="inlineStr"/>
+      <c r="K1431" t="inlineStr"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="1" t="n">
+        <v>46152.39665454861</v>
+      </c>
+      <c r="B1432" t="n">
+        <v>262.28</v>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr"/>
+      <c r="E1432" t="inlineStr"/>
+      <c r="F1432" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1432" t="inlineStr"/>
+      <c r="H1432" t="n">
+        <v>69</v>
+      </c>
+      <c r="I1432" t="n">
+        <v>148</v>
+      </c>
+      <c r="J1432" t="inlineStr"/>
+      <c r="K1432" t="inlineStr"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>46152.39665802084</v>
+      </c>
+      <c r="B1433" t="n">
+        <v>262.579</v>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr"/>
+      <c r="E1433" t="inlineStr"/>
+      <c r="F1433" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1433" t="inlineStr"/>
+      <c r="H1433" t="n">
+        <v>70</v>
+      </c>
+      <c r="I1433" t="n">
+        <v>149</v>
+      </c>
+      <c r="J1433" t="inlineStr"/>
+      <c r="K1433" t="inlineStr"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="1" t="n">
+        <v>46152.39669663194</v>
+      </c>
+      <c r="B1434" t="n">
+        <v>265.916</v>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr"/>
+      <c r="E1434" t="inlineStr"/>
+      <c r="F1434" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1434" t="inlineStr"/>
+      <c r="H1434" t="n">
+        <v>71</v>
+      </c>
+      <c r="I1434" t="n">
+        <v>150</v>
+      </c>
+      <c r="J1434" t="inlineStr"/>
+      <c r="K1434" t="inlineStr"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="1" t="n">
+        <v>46152.39671228009</v>
+      </c>
+      <c r="B1435" t="n">
+        <v>267.268</v>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr"/>
+      <c r="E1435" t="inlineStr"/>
+      <c r="F1435" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1435" t="inlineStr"/>
+      <c r="H1435" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1435" t="n">
+        <v>151</v>
+      </c>
+      <c r="J1435" t="inlineStr"/>
+      <c r="K1435" t="inlineStr"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="1" t="n">
+        <v>46152.39672921296</v>
+      </c>
+      <c r="B1436" t="n">
+        <v>268.731</v>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr"/>
+      <c r="E1436" t="inlineStr"/>
+      <c r="F1436" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1436" t="inlineStr"/>
+      <c r="H1436" t="n">
+        <v>73</v>
+      </c>
+      <c r="I1436" t="n">
+        <v>152</v>
+      </c>
+      <c r="J1436" t="inlineStr"/>
+      <c r="K1436" t="inlineStr"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="1" t="n">
+        <v>46152.39673364583</v>
+      </c>
+      <c r="B1437" t="n">
+        <v>269.113</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr"/>
+      <c r="E1437" t="inlineStr"/>
+      <c r="F1437" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1437" t="inlineStr"/>
+      <c r="H1437" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1437" t="n">
+        <v>153</v>
+      </c>
+      <c r="J1437" t="inlineStr"/>
+      <c r="K1437" t="inlineStr"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="1" t="n">
+        <v>46152.39674875</v>
+      </c>
+      <c r="B1438" t="n">
+        <v>270.419</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1438" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1438" t="inlineStr"/>
+      <c r="G1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1438" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1438" t="inlineStr"/>
+      <c r="K1438" t="inlineStr"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="1" t="n">
+        <v>46152.39677071759</v>
+      </c>
+      <c r="B1439" t="n">
+        <v>272.317</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr"/>
+      <c r="E1439" t="inlineStr"/>
+      <c r="F1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1439" t="inlineStr"/>
+      <c r="H1439" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1439" t="n">
+        <v>154</v>
+      </c>
+      <c r="J1439" t="inlineStr"/>
+      <c r="K1439" t="inlineStr"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="1" t="n">
+        <v>46152.39681432871</v>
+      </c>
+      <c r="B1440" t="n">
+        <v>276.085</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr"/>
+      <c r="E1440" t="inlineStr"/>
+      <c r="F1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1440" t="inlineStr"/>
+      <c r="H1440" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1440" t="n">
+        <v>155</v>
+      </c>
+      <c r="J1440" t="inlineStr"/>
+      <c r="K1440" t="inlineStr"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="1" t="n">
+        <v>46152.39681706019</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>276.321</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr"/>
+      <c r="E1441" t="inlineStr"/>
+      <c r="F1441" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1441" t="inlineStr"/>
+      <c r="H1441" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1441" t="n">
+        <v>156</v>
+      </c>
+      <c r="J1441" t="inlineStr"/>
+      <c r="K1441" t="inlineStr"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="1" t="n">
+        <v>46152.39682153935</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>276.708</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr"/>
+      <c r="E1442" t="inlineStr"/>
+      <c r="F1442" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1442" t="inlineStr"/>
+      <c r="H1442" t="n">
+        <v>74</v>
+      </c>
+      <c r="I1442" t="n">
+        <v>157</v>
+      </c>
+      <c r="J1442" t="inlineStr"/>
+      <c r="K1442" t="inlineStr"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="1" t="n">
+        <v>46152.39683670139</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>278.018</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr"/>
+      <c r="E1443" t="inlineStr"/>
+      <c r="F1443" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1443" t="inlineStr"/>
+      <c r="H1443" t="n">
+        <v>75</v>
+      </c>
+      <c r="I1443" t="n">
+        <v>158</v>
+      </c>
+      <c r="J1443" t="inlineStr"/>
+      <c r="K1443" t="inlineStr"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="1" t="n">
+        <v>46152.39684321759</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>278.581</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr"/>
+      <c r="E1444" t="inlineStr"/>
+      <c r="F1444" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1444" t="inlineStr"/>
+      <c r="H1444" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1444" t="n">
+        <v>159</v>
+      </c>
+      <c r="J1444" t="inlineStr"/>
+      <c r="K1444" t="inlineStr"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="1" t="n">
+        <v>46152.39685012731</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>279.178</v>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr"/>
+      <c r="E1445" t="inlineStr"/>
+      <c r="F1445" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1445" t="inlineStr"/>
+      <c r="H1445" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1445" t="n">
+        <v>160</v>
+      </c>
+      <c r="J1445" t="inlineStr"/>
+      <c r="K1445" t="inlineStr"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="1" t="n">
+        <v>46152.39686234954</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>280.234</v>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1446" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1446" t="inlineStr"/>
+      <c r="G1446" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1446" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1446" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1446" t="inlineStr"/>
+      <c r="K1446" t="inlineStr"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="1" t="n">
+        <v>46152.39688101852</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>281.847</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr"/>
+      <c r="E1447" t="inlineStr"/>
+      <c r="F1447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1447" t="inlineStr"/>
+      <c r="H1447" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1447" t="n">
+        <v>161</v>
+      </c>
+      <c r="J1447" t="inlineStr"/>
+      <c r="K1447" t="inlineStr"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="1" t="n">
+        <v>46152.39688413194</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>282.115</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr"/>
+      <c r="E1448" t="inlineStr"/>
+      <c r="F1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1448" t="inlineStr"/>
+      <c r="H1448" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1448" t="n">
+        <v>162</v>
+      </c>
+      <c r="J1448" t="inlineStr"/>
+      <c r="K1448" t="inlineStr"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46152.39689074074</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>282.687</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr"/>
+      <c r="E1449" t="inlineStr"/>
+      <c r="F1449" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1449" t="inlineStr"/>
+      <c r="H1449" t="n">
+        <v>76</v>
+      </c>
+      <c r="I1449" t="n">
+        <v>163</v>
+      </c>
+      <c r="J1449" t="inlineStr"/>
+      <c r="K1449" t="inlineStr"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46152.39689564815</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>283.111</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr"/>
+      <c r="E1450" t="inlineStr"/>
+      <c r="F1450" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1450" t="inlineStr"/>
+      <c r="H1450" t="n">
+        <v>77</v>
+      </c>
+      <c r="I1450" t="n">
+        <v>164</v>
+      </c>
+      <c r="J1450" t="inlineStr"/>
+      <c r="K1450" t="inlineStr"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46152.39689987269</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>283.475</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr"/>
+      <c r="E1451" t="inlineStr"/>
+      <c r="F1451" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1451" t="inlineStr"/>
+      <c r="H1451" t="n">
+        <v>78</v>
+      </c>
+      <c r="I1451" t="n">
+        <v>165</v>
+      </c>
+      <c r="J1451" t="inlineStr"/>
+      <c r="K1451" t="inlineStr"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46152.39690353009</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>283.792</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr"/>
+      <c r="E1452" t="inlineStr"/>
+      <c r="F1452" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1452" t="inlineStr"/>
+      <c r="H1452" t="n">
+        <v>79</v>
+      </c>
+      <c r="I1452" t="n">
+        <v>166</v>
+      </c>
+      <c r="J1452" t="inlineStr"/>
+      <c r="K1452" t="inlineStr"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46152.39690770833</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>284.153</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr"/>
+      <c r="E1453" t="inlineStr"/>
+      <c r="F1453" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1453" t="inlineStr"/>
+      <c r="H1453" t="n">
+        <v>80</v>
+      </c>
+      <c r="I1453" t="n">
+        <v>167</v>
+      </c>
+      <c r="J1453" t="inlineStr"/>
+      <c r="K1453" t="inlineStr"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46152.396923125</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>285.485</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr"/>
+      <c r="E1454" t="inlineStr"/>
+      <c r="F1454" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="n">
+        <v>81</v>
+      </c>
+      <c r="I1454" t="n">
+        <v>168</v>
+      </c>
+      <c r="J1454" t="inlineStr"/>
+      <c r="K1454" t="inlineStr"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="1" t="n">
+        <v>46152.39692715277</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>285.833</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr"/>
+      <c r="E1455" t="inlineStr"/>
+      <c r="F1455" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1455" t="inlineStr"/>
+      <c r="H1455" t="n">
+        <v>82</v>
+      </c>
+      <c r="I1455" t="n">
+        <v>169</v>
+      </c>
+      <c r="J1455" t="inlineStr"/>
+      <c r="K1455" t="inlineStr"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46152.39693061342</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>286.132</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr"/>
+      <c r="E1456" t="inlineStr"/>
+      <c r="F1456" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1456" t="inlineStr"/>
+      <c r="H1456" t="n">
+        <v>83</v>
+      </c>
+      <c r="I1456" t="n">
+        <v>170</v>
+      </c>
+      <c r="J1456" t="inlineStr"/>
+      <c r="K1456" t="inlineStr"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46152.39695806713</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>288.504</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr"/>
+      <c r="E1457" t="inlineStr"/>
+      <c r="F1457" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1457" t="inlineStr"/>
+      <c r="H1457" t="n">
+        <v>84</v>
+      </c>
+      <c r="I1457" t="n">
+        <v>171</v>
+      </c>
+      <c r="J1457" t="inlineStr"/>
+      <c r="K1457" t="inlineStr"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46152.39696563657</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>289.157</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr"/>
+      <c r="E1458" t="inlineStr"/>
+      <c r="F1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1458" t="inlineStr"/>
+      <c r="H1458" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1458" t="n">
+        <v>172</v>
+      </c>
+      <c r="J1458" t="inlineStr"/>
+      <c r="K1458" t="inlineStr"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46152.39696965278</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>289.505</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr"/>
+      <c r="E1459" t="inlineStr"/>
+      <c r="F1459" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1459" t="inlineStr"/>
+      <c r="H1459" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1459" t="n">
+        <v>173</v>
+      </c>
+      <c r="J1459" t="inlineStr"/>
+      <c r="K1459" t="inlineStr"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46152.3969743287</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>289.909</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr"/>
+      <c r="E1460" t="inlineStr"/>
+      <c r="F1460" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1460" t="n">
+        <v>174</v>
+      </c>
+      <c r="J1460" t="inlineStr"/>
+      <c r="K1460" t="inlineStr"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46152.39697935186</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>290.343</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr"/>
+      <c r="E1461" t="inlineStr"/>
+      <c r="F1461" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="n">
+        <v>86</v>
+      </c>
+      <c r="I1461" t="n">
+        <v>175</v>
+      </c>
+      <c r="J1461" t="inlineStr"/>
+      <c r="K1461" t="inlineStr"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46152.39699662037</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>291.835</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1462" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1462" t="inlineStr"/>
+      <c r="G1462" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>86</v>
+      </c>
+      <c r="I1462" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1462" t="inlineStr"/>
+      <c r="K1462" t="inlineStr"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>46152.39702267361</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>294.085</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr"/>
+      <c r="E1463" t="inlineStr"/>
+      <c r="F1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1463" t="inlineStr"/>
+      <c r="H1463" t="n">
+        <v>86</v>
+      </c>
+      <c r="I1463" t="n">
+        <v>176</v>
+      </c>
+      <c r="J1463" t="inlineStr"/>
+      <c r="K1463" t="inlineStr"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>46152.39703490741</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>295.143</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr"/>
+      <c r="E1464" t="inlineStr"/>
+      <c r="F1464" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1464" t="inlineStr"/>
+      <c r="H1464" t="n">
+        <v>86</v>
+      </c>
+      <c r="I1464" t="n">
+        <v>177</v>
+      </c>
+      <c r="J1464" t="inlineStr"/>
+      <c r="K1464" t="inlineStr"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46152.39704986111</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>296.435</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr"/>
+      <c r="E1465" t="inlineStr"/>
+      <c r="F1465" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1465" t="inlineStr"/>
+      <c r="H1465" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1465" t="n">
+        <v>178</v>
+      </c>
+      <c r="J1465" t="inlineStr"/>
+      <c r="K1465" t="inlineStr"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46152.3970531713</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>296.721</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr"/>
+      <c r="E1466" t="inlineStr"/>
+      <c r="F1466" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1466" t="inlineStr"/>
+      <c r="H1466" t="n">
+        <v>86</v>
+      </c>
+      <c r="I1466" t="n">
+        <v>179</v>
+      </c>
+      <c r="J1466" t="inlineStr"/>
+      <c r="K1466" t="inlineStr"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46152.39706677083</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>297.896</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr"/>
+      <c r="E1467" t="inlineStr"/>
+      <c r="F1467" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1467" t="n">
+        <v>180</v>
+      </c>
+      <c r="J1467" t="inlineStr"/>
+      <c r="K1467" t="inlineStr"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46152.39707309028</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>298.442</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr"/>
+      <c r="E1468" t="inlineStr"/>
+      <c r="F1468" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1468" t="inlineStr"/>
+      <c r="H1468" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1468" t="n">
+        <v>181</v>
+      </c>
+      <c r="J1468" t="inlineStr"/>
+      <c r="K1468" t="inlineStr"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46152.39707868056</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>298.925</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr"/>
+      <c r="E1469" t="inlineStr"/>
+      <c r="F1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1469" t="inlineStr"/>
+      <c r="H1469" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1469" t="n">
+        <v>182</v>
+      </c>
+      <c r="J1469" t="inlineStr"/>
+      <c r="K1469" t="inlineStr"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46152.39708598379</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>299.555</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1470" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1470" t="inlineStr"/>
+      <c r="G1470" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1470" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1470" t="inlineStr"/>
+      <c r="K1470" t="inlineStr"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>46152.39708674768</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>299.622</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr"/>
+      <c r="E1471" t="inlineStr"/>
+      <c r="F1471" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1471" t="inlineStr"/>
+      <c r="H1471" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1471" t="n">
+        <v>183</v>
+      </c>
+      <c r="J1471" t="inlineStr"/>
+      <c r="K1471" t="inlineStr"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>46152.39709299769</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>300.162</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr"/>
+      <c r="E1472" t="inlineStr"/>
+      <c r="F1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1472" t="inlineStr"/>
+      <c r="H1472" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1472" t="n">
+        <v>184</v>
+      </c>
+      <c r="J1472" t="inlineStr"/>
+      <c r="K1472" t="inlineStr"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46152.39709788194</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>300.583</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr"/>
+      <c r="E1473" t="inlineStr"/>
+      <c r="F1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1473" t="inlineStr"/>
+      <c r="H1473" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1473" t="n">
+        <v>185</v>
+      </c>
+      <c r="J1473" t="inlineStr"/>
+      <c r="K1473" t="inlineStr"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46152.39711327546</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>301.914</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr"/>
+      <c r="E1474" t="inlineStr"/>
+      <c r="F1474" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1474" t="n">
+        <v>186</v>
+      </c>
+      <c r="J1474" t="inlineStr"/>
+      <c r="K1474" t="inlineStr"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46152.39712818287</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>303.202</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr"/>
+      <c r="E1475" t="inlineStr"/>
+      <c r="F1475" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1475" t="inlineStr"/>
+      <c r="H1475" t="n">
+        <v>88</v>
+      </c>
+      <c r="I1475" t="n">
+        <v>187</v>
+      </c>
+      <c r="J1475" t="inlineStr"/>
+      <c r="K1475" t="inlineStr"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46152.39714284722</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>304.469</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr"/>
+      <c r="E1476" t="inlineStr"/>
+      <c r="F1476" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1476" t="inlineStr"/>
+      <c r="H1476" t="n">
+        <v>89</v>
+      </c>
+      <c r="I1476" t="n">
+        <v>188</v>
+      </c>
+      <c r="J1476" t="inlineStr"/>
+      <c r="K1476" t="inlineStr"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="1" t="n">
+        <v>46152.39715748843</v>
+      </c>
+      <c r="B1477" t="n">
+        <v>305.734</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr"/>
+      <c r="E1477" t="inlineStr"/>
+      <c r="F1477" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1477" t="inlineStr"/>
+      <c r="H1477" t="n">
+        <v>90</v>
+      </c>
+      <c r="I1477" t="n">
+        <v>189</v>
+      </c>
+      <c r="J1477" t="inlineStr"/>
+      <c r="K1477" t="inlineStr"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="1" t="n">
+        <v>46152.39717200232</v>
+      </c>
+      <c r="B1478" t="n">
+        <v>306.988</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr"/>
+      <c r="E1478" t="inlineStr"/>
+      <c r="F1478" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1478" t="inlineStr"/>
+      <c r="H1478" t="n">
+        <v>91</v>
+      </c>
+      <c r="I1478" t="n">
+        <v>190</v>
+      </c>
+      <c r="J1478" t="inlineStr"/>
+      <c r="K1478" t="inlineStr"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="n">
+        <v>46152.39718650463</v>
+      </c>
+      <c r="B1479" t="n">
+        <v>308.24</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr"/>
+      <c r="E1479" t="inlineStr"/>
+      <c r="F1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1479" t="inlineStr"/>
+      <c r="H1479" t="n">
+        <v>92</v>
+      </c>
+      <c r="I1479" t="n">
+        <v>191</v>
+      </c>
+      <c r="J1479" t="inlineStr"/>
+      <c r="K1479" t="inlineStr"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="n">
+        <v>46152.39718974537</v>
+      </c>
+      <c r="B1480" t="n">
+        <v>308.52</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr"/>
+      <c r="E1480" t="inlineStr"/>
+      <c r="F1480" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="n">
+        <v>92</v>
+      </c>
+      <c r="I1480" t="n">
+        <v>192</v>
+      </c>
+      <c r="J1480" t="inlineStr"/>
+      <c r="K1480" t="inlineStr"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>46152.39719435186</v>
+      </c>
+      <c r="B1481" t="n">
+        <v>308.919</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr"/>
+      <c r="E1481" t="inlineStr"/>
+      <c r="F1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1481" t="inlineStr"/>
+      <c r="H1481" t="n">
+        <v>92</v>
+      </c>
+      <c r="I1481" t="n">
+        <v>193</v>
+      </c>
+      <c r="J1481" t="inlineStr"/>
+      <c r="K1481" t="inlineStr"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="n">
+        <v>46152.39720521991</v>
+      </c>
+      <c r="B1482" t="n">
+        <v>309.858</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr"/>
+      <c r="E1482" t="inlineStr"/>
+      <c r="F1482" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1482" t="inlineStr"/>
+      <c r="H1482" t="n">
+        <v>93</v>
+      </c>
+      <c r="I1482" t="n">
+        <v>194</v>
+      </c>
+      <c r="J1482" t="inlineStr"/>
+      <c r="K1482" t="inlineStr"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="1" t="n">
+        <v>46152.39722199074</v>
+      </c>
+      <c r="B1483" t="n">
+        <v>311.306</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1483" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1483" t="inlineStr"/>
+      <c r="G1483" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>93</v>
+      </c>
+      <c r="I1483" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1483" t="inlineStr"/>
+      <c r="K1483" t="inlineStr"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="1" t="n">
+        <v>46152.39724582176</v>
+      </c>
+      <c r="B1484" t="n">
+        <v>313.366</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr"/>
+      <c r="E1484" t="inlineStr"/>
+      <c r="F1484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1484" t="inlineStr"/>
+      <c r="H1484" t="n">
+        <v>93</v>
+      </c>
+      <c r="I1484" t="n">
+        <v>195</v>
+      </c>
+      <c r="J1484" t="inlineStr"/>
+      <c r="K1484" t="inlineStr"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="1" t="n">
+        <v>46152.39725706018</v>
+      </c>
+      <c r="B1485" t="n">
+        <v>314.336</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr"/>
+      <c r="E1485" t="inlineStr"/>
+      <c r="F1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1485" t="inlineStr"/>
+      <c r="H1485" t="n">
+        <v>93</v>
+      </c>
+      <c r="I1485" t="n">
+        <v>196</v>
+      </c>
+      <c r="J1485" t="inlineStr"/>
+      <c r="K1485" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="1" t="n">
+        <v>46152.3972721875</v>
+      </c>
+      <c r="B1486" t="n">
+        <v>315.643</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr"/>
+      <c r="E1486" t="inlineStr"/>
+      <c r="F1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1486" t="inlineStr"/>
+      <c r="H1486" t="n">
+        <v>94</v>
+      </c>
+      <c r="I1486" t="n">
+        <v>197</v>
+      </c>
+      <c r="J1486" t="inlineStr"/>
+      <c r="K1486" t="inlineStr"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="1" t="n">
+        <v>46152.39727583333</v>
+      </c>
+      <c r="B1487" t="n">
+        <v>315.958</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr"/>
+      <c r="E1487" t="inlineStr"/>
+      <c r="F1487" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="n">
+        <v>95</v>
+      </c>
+      <c r="I1487" t="n">
+        <v>198</v>
+      </c>
+      <c r="J1487" t="inlineStr"/>
+      <c r="K1487" t="inlineStr"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="1" t="n">
+        <v>46152.39728018519</v>
+      </c>
+      <c r="B1488" t="n">
+        <v>316.335</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr"/>
+      <c r="E1488" t="inlineStr"/>
+      <c r="F1488" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1488" t="inlineStr"/>
+      <c r="H1488" t="n">
+        <v>96</v>
+      </c>
+      <c r="I1488" t="n">
+        <v>199</v>
+      </c>
+      <c r="J1488" t="inlineStr"/>
+      <c r="K1488" t="inlineStr"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>46152.39728284723</v>
+      </c>
+      <c r="B1489" t="n">
+        <v>316.565</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr"/>
+      <c r="E1489" t="inlineStr"/>
+      <c r="F1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1489" t="inlineStr"/>
+      <c r="H1489" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1489" t="n">
+        <v>200</v>
+      </c>
+      <c r="J1489" t="inlineStr"/>
+      <c r="K1489" t="inlineStr"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>46152.39728885417</v>
+      </c>
+      <c r="B1490" t="n">
+        <v>317.084</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr"/>
+      <c r="E1490" t="inlineStr"/>
+      <c r="F1490" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1490" t="inlineStr"/>
+      <c r="H1490" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1490" t="n">
+        <v>201</v>
+      </c>
+      <c r="J1490" t="inlineStr"/>
+      <c r="K1490" t="inlineStr"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="n">
+        <v>46152.39730113426</v>
+      </c>
+      <c r="B1491" t="n">
+        <v>318.144</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1491" t="inlineStr"/>
+      <c r="G1491" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1491" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1491" t="inlineStr"/>
+      <c r="K1491" t="inlineStr"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="n">
+        <v>46152.39731108796</v>
+      </c>
+      <c r="B1492" t="n">
+        <v>319.005</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr"/>
+      <c r="E1492" t="inlineStr"/>
+      <c r="F1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1492" t="inlineStr"/>
+      <c r="H1492" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1492" t="n">
+        <v>202</v>
+      </c>
+      <c r="J1492" t="inlineStr"/>
+      <c r="K1492" t="inlineStr"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>46152.39731461806</v>
+      </c>
+      <c r="B1493" t="n">
+        <v>319.31</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr"/>
+      <c r="E1493" t="inlineStr"/>
+      <c r="F1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1493" t="n">
+        <v>203</v>
+      </c>
+      <c r="J1493" t="inlineStr"/>
+      <c r="K1493" t="inlineStr"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="n">
+        <v>46152.39732929398</v>
+      </c>
+      <c r="B1494" t="n">
+        <v>320.578</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr"/>
+      <c r="E1494" t="inlineStr"/>
+      <c r="F1494" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="n">
+        <v>97</v>
+      </c>
+      <c r="I1494" t="n">
+        <v>204</v>
+      </c>
+      <c r="J1494" t="inlineStr"/>
+      <c r="K1494" t="inlineStr"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="n">
+        <v>46152.39733259259</v>
+      </c>
+      <c r="B1495" t="n">
+        <v>320.863</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr"/>
+      <c r="E1495" t="inlineStr"/>
+      <c r="F1495" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="n">
+        <v>98</v>
+      </c>
+      <c r="I1495" t="n">
+        <v>205</v>
+      </c>
+      <c r="J1495" t="inlineStr"/>
+      <c r="K1495" t="inlineStr"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46152.39738300926</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>325.219</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr"/>
+      <c r="E1496" t="inlineStr"/>
+      <c r="F1496" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="n">
+        <v>99</v>
+      </c>
+      <c r="I1496" t="n">
+        <v>206</v>
+      </c>
+      <c r="J1496" t="inlineStr"/>
+      <c r="K1496" t="inlineStr"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46152.39361890046</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>325.253</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr"/>
+      <c r="E1497" t="inlineStr"/>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>100</v>
+      </c>
+      <c r="I1497" t="n">
+        <v>206</v>
+      </c>
+      <c r="J1497" t="inlineStr"/>
+      <c r="K1497" t="inlineStr"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>46152.4860208329</v>
+      </c>
+      <c r="B1498" t="n">
+        <v>23.503</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr"/>
+      <c r="E1498" t="inlineStr"/>
+      <c r="F1498" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1498" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1498" t="inlineStr"/>
+      <c r="K1498" t="inlineStr"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46152.48603587653</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>24.803</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr"/>
+      <c r="E1499" t="inlineStr"/>
+      <c r="F1499" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1499" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1499" t="inlineStr"/>
+      <c r="K1499" t="inlineStr"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>46152.48605534658</v>
+      </c>
+      <c r="B1500" t="n">
+        <v>26.485</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr"/>
+      <c r="E1500" t="inlineStr"/>
+      <c r="F1500" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1500" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1500" t="inlineStr"/>
+      <c r="K1500" t="inlineStr"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="n">
+        <v>46152.48606861251</v>
+      </c>
+      <c r="B1501" t="n">
+        <v>27.631</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr"/>
+      <c r="E1501" t="inlineStr"/>
+      <c r="F1501" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1501" t="inlineStr"/>
+      <c r="H1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1501" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1501" t="inlineStr"/>
+      <c r="K1501" t="inlineStr"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>46152.48608603628</v>
+      </c>
+      <c r="B1502" t="n">
+        <v>29.136</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr"/>
+      <c r="E1502" t="inlineStr"/>
+      <c r="F1502" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1502" t="inlineStr"/>
+      <c r="H1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1502" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1502" t="inlineStr"/>
+      <c r="K1502" t="inlineStr"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46152.48609654051</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>30.044</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr"/>
+      <c r="E1503" t="inlineStr"/>
+      <c r="F1503" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1503" t="inlineStr"/>
+      <c r="H1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1503" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1503" t="inlineStr"/>
+      <c r="K1503" t="inlineStr"/>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46152.48610705922</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>30.953</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr"/>
+      <c r="E1504" t="inlineStr"/>
+      <c r="F1504" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1504" t="inlineStr"/>
+      <c r="H1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1504" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1504" t="inlineStr"/>
+      <c r="K1504" t="inlineStr"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46152.48611772662</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>31.875</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr"/>
+      <c r="E1505" t="inlineStr"/>
+      <c r="F1505" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1505" t="inlineStr"/>
+      <c r="H1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1505" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1505" t="inlineStr"/>
+      <c r="K1505" t="inlineStr"/>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46152.48613876874</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>33.693</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr"/>
+      <c r="E1506" t="inlineStr"/>
+      <c r="F1506" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1506" t="inlineStr"/>
+      <c r="H1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1506" t="n">
+        <v>9</v>
+      </c>
+      <c r="J1506" t="inlineStr"/>
+      <c r="K1506" t="inlineStr"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46152.48615404638</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>35.013</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr"/>
+      <c r="E1507" t="inlineStr"/>
+      <c r="F1507" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1507" t="inlineStr"/>
+      <c r="H1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1507" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1507" t="inlineStr"/>
+      <c r="K1507" t="inlineStr"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>46152.48616494132</v>
+      </c>
+      <c r="B1508" t="n">
+        <v>35.954</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr"/>
+      <c r="E1508" t="inlineStr"/>
+      <c r="F1508" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1508" t="inlineStr"/>
+      <c r="H1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1508" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1508" t="inlineStr"/>
+      <c r="K1508" t="inlineStr"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46152.48618017245</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr"/>
+      <c r="E1509" t="inlineStr"/>
+      <c r="F1509" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1509" t="inlineStr"/>
+      <c r="H1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1509" t="n">
+        <v>12</v>
+      </c>
+      <c r="J1509" t="inlineStr"/>
+      <c r="K1509" t="inlineStr"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>46152.4861900321</v>
+      </c>
+      <c r="B1510" t="n">
+        <v>38.122</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr"/>
+      <c r="E1510" t="inlineStr"/>
+      <c r="F1510" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1510" t="inlineStr"/>
+      <c r="H1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1510" t="n">
+        <v>13</v>
+      </c>
+      <c r="J1510" t="inlineStr"/>
+      <c r="K1510" t="inlineStr"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46152.48624368882</v>
+      </c>
+      <c r="B1511" t="n">
+        <v>42.758</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr"/>
+      <c r="E1511" t="inlineStr"/>
+      <c r="F1511" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1511" t="inlineStr"/>
+      <c r="H1511" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1511" t="n">
+        <v>14</v>
+      </c>
+      <c r="J1511" t="inlineStr"/>
+      <c r="K1511" t="inlineStr"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>46152.48625136925</v>
+      </c>
+      <c r="B1512" t="n">
+        <v>43.421</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr"/>
+      <c r="E1512" t="inlineStr"/>
+      <c r="F1512" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1512" t="inlineStr"/>
+      <c r="H1512" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1512" t="n">
+        <v>15</v>
+      </c>
+      <c r="J1512" t="inlineStr"/>
+      <c r="K1512" t="inlineStr"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46152.48625538933</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>43.769</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>MrBall</t>
+        </is>
+      </c>
+      <c r="E1513" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1513" t="inlineStr"/>
+      <c r="G1513" t="b">
+        <v>1</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1513" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1513" t="inlineStr"/>
+      <c r="K1513" t="inlineStr"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>46152.48628717878</v>
+      </c>
+      <c r="B1514" t="n">
+        <v>46.515</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr"/>
+      <c r="E1514" t="inlineStr"/>
+      <c r="F1514" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1514" t="inlineStr"/>
+      <c r="H1514" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1514" t="n">
+        <v>16</v>
+      </c>
+      <c r="J1514" t="inlineStr"/>
+      <c r="K1514" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="n">
+        <v>46152.48630565045</v>
+      </c>
+      <c r="B1515" t="n">
+        <v>48.111</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>TurnRight</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr"/>
+      <c r="E1515" t="inlineStr"/>
+      <c r="F1515" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1515" t="inlineStr"/>
+      <c r="H1515" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1515" t="n">
+        <v>17</v>
+      </c>
+      <c r="J1515" t="inlineStr"/>
+      <c r="K1515" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="n">
+        <v>46152.48631347169</v>
+      </c>
+      <c r="B1516" t="n">
+        <v>48.787</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr"/>
+      <c r="E1516" t="inlineStr"/>
+      <c r="F1516" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1516" t="inlineStr"/>
+      <c r="H1516" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1516" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1516" t="inlineStr"/>
+      <c r="K1516" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="n">
+        <v>46152.48631913447</v>
+      </c>
+      <c r="B1517" t="n">
+        <v>49.276</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr"/>
+      <c r="E1517" t="inlineStr"/>
+      <c r="F1517" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1517" t="inlineStr"/>
+      <c r="H1517" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1517" t="n">
+        <v>19</v>
+      </c>
+      <c r="J1517" t="inlineStr"/>
+      <c r="K1517" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="n">
+        <v>46152.48636397401</v>
+      </c>
+      <c r="B1518" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>TurnLeft</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr"/>
+      <c r="E1518" t="inlineStr"/>
+      <c r="F1518" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1518" t="inlineStr"/>
+      <c r="H1518" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1518" t="n">
+        <v>20</v>
+      </c>
+      <c r="J1518" t="inlineStr"/>
+      <c r="K1518" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="n">
+        <v>46152.48637216113</v>
+      </c>
+      <c r="B1519" t="n">
+        <v>53.858</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>MrTemp</t>
+        </is>
+      </c>
+      <c r="E1519" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1519" t="inlineStr"/>
+      <c r="G1519" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1519" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1519" t="inlineStr"/>
+      <c r="K1519" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>46152.48637252948</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr"/>
+      <c r="E1520" t="inlineStr"/>
+      <c r="F1520" t="b">
+        <v>1</v>
+      </c>
+      <c r="G1520" t="inlineStr"/>
+      <c r="H1520" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1520" t="n">
+        <v>21</v>
+      </c>
+      <c r="J1520" t="inlineStr"/>
+      <c r="K1520" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="n">
+        <v>46152.48574880597</v>
+      </c>
+      <c r="B1521" t="n">
+        <v>54.673</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr"/>
+      <c r="E1521" t="inlineStr"/>
+      <c r="F1521" t="inlineStr"/>
+      <c r="G1521" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1521" t="n">
+        <v>21</v>
+      </c>
+      <c r="J1521" t="inlineStr"/>
+      <c r="K1521" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
